--- a/songs/InTheDark_v1/quelle/struktur.xlsx
+++ b/songs/InTheDark_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>13</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>116</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>BLACK</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(7500, 5)   (Matrix: progScrollText("In the dark by Purple Disco Machine", 23000, 90, getRandomColor(), 4))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7500, 5)   (Matrix: progScrollText("In the dark by Purple Disco Machine", 23000, 90, getRandomColor(), 4))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>intro+verse 1</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(33090, 10, 5000)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(33090, 10, 5000)</t>
         </is>
@@ -572,13 +593,19 @@
           <t>bridge 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(16550, 12, 515)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16550, 12, 515)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16550, 1035, 14, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 1035, 14, 5, 26, 5, true, 3)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(16540, 4, 16)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(16540, 4, 16)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>bridge 2</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(16550, 18, 515, true)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16550, 18, 515, true)</t>
         </is>
@@ -656,13 +701,20 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16550, 1035, 20, 5, 26, 5, false, 4)
+! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = 0</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 1035, 20, 5, 26, 5, false, 4)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = 0</t>
@@ -678,13 +730,20 @@
           <t>am i going under</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16550, 22, 50, true, false)
+! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = ESaite_Dis</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16550, 22, 50, true, false)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = ESaite_Dis</t>
@@ -700,13 +759,20 @@
           <t>bass solo</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixHorizontal(16550, 24, 70, true)
+! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = ESaite_Dis</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(16550, 24, 70, true)
 ! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = ESaite_Dis</t>
@@ -722,13 +788,20 @@
           <t>chrous 3</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16550, 515, 26, 5, 26, 5, true, 3)
+! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = 0</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 515, 26, 5, 26, 5, true, 3)
 ! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = 0</t>
@@ -744,13 +817,19 @@
           <t>chorus 4</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(16550, 8, 28)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16550, 8, 28)</t>
         </is>
@@ -765,13 +844,19 @@
           <t>fade out</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(6200, 30, 5000)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(6200, 30, 5000)</t>
         </is>
@@ -791,10 +876,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/InTheDark_v1/quelle/struktur.xlsx
+++ b/songs/InTheDark_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>

--- a/songs/InTheDark_v1/quelle/struktur.xlsx
+++ b/songs/InTheDark_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7500, 5)   (Matrix: progScrollText("In the dark by Purple Disco Machine", 23000, 90, getRandomColor(), 4))</t>
         </is>
@@ -573,12 +583,18 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>16 Takte ein Effekt sind lang. Szene Glow, ROYAL, Farbwanderung (triad, 2 Takte), auf 60 % gedimmt - "in the dark".
+Besser: bei Takt 13 eine eigene Zeile "verse 1" anlegen - dann ab dort Szene Verse (Puls im Beat).</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(33090, 10, 5000)</t>
         </is>
@@ -600,12 +616,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors Wave, SUNSET, soft 60: die Farbe wandert pro Beat weich von Gerät zu Gerät. Letzter Takt weißer Strobo (tail 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16550, 12, 515)</t>
         </is>
@@ -627,12 +648,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, NEON, Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 1035, 14, 5, 26, 5, true, 3)</t>
         </is>
@@ -654,12 +680,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip Scroll, ROYAL: Helix auf der Matrix, alle anderen pulsieren einmal je Takt. Weich eingeblendet (fade, 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progPalette(16540, 4, 16)</t>
         </is>
@@ -681,12 +712,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, SUNSET: Bühnenhälften blitzen abwechselnd im Beat. Letzter Takt weißer Strobo (tail 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16550, 18, 515, true)</t>
         </is>
@@ -709,12 +745,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, NEON wie chorus 1, dazu blitzen die Lampen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 1035, 20, 5, 26, 5, false, 4)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = 0</t>
@@ -738,12 +779,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben (passt zum Text), in BLUE und weich eingeblendet (fade, 4 Beats); Farbwanderung nach ICE.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16550, 22, 50, true, false)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = ESaite_Dis</t>
@@ -767,12 +813,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Solo Bass, NEON: zwei Kometen laufen um den Bass, alle anderen atmen dunkel. In den letzten 2 Takten baut sich ein Blinder auf (blendet 2 Takte ein, voll auf Takt 77).</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(16550, 24, 70, true)
 ! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = ESaite_Dis</t>
@@ -796,12 +847,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, SUNSET - eine Stufe wärmer, der Blinder vom Bass-Solo steht auf dem Einsatz.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 515, 26, 5, 26, 5, true, 3)
 ! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = 0</t>
@@ -824,12 +880,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE; drei kurze Blinder Ende des 4. Takts (Takt 88,5 / 88,75 / 89); starker Blinder auf der letzten Viertel (Takt 92,75), klingt ins Fade-out aus (carry).</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16550, 8, 28)</t>
         </is>
@@ -851,12 +912,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fadeout, ROYAL: blendet über die 3 Takte weich nach Schwarz.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(6200, 30, 5000)</t>
         </is>
@@ -876,10 +942,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/InTheDark_v1/quelle/struktur.xlsx
+++ b/songs/InTheDark_v1/quelle/struktur.xlsx
@@ -433,10 +433,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" collapsed="1">
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
@@ -550,8 +550,8 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progBlack(7500, 5)   (Matrix: progScrollText("In the dark by Purple Disco Machine", 23000, 90, getRandomColor(), 4))</t>
+          <t>progBlack(7500, 3), Farben SCHEME_ROYAL
+Alles schwarz bis zum Einsatz (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
@@ -567,385 +567,4820 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="n"/>
+    </row>
+    <row r="8" hidden="1" outlineLevel="2">
+      <c r="A8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="2">
+      <c r="A9" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6" t="n"/>
+    </row>
+    <row r="11" hidden="1" outlineLevel="2">
+      <c r="A11" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="n"/>
+    </row>
+    <row r="12" hidden="1" outlineLevel="2">
+      <c r="A12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="n"/>
+    </row>
+    <row r="13" hidden="1" outlineLevel="2">
+      <c r="A13" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" hidden="1" outlineLevel="2">
+      <c r="A15" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" hidden="1" outlineLevel="2">
+      <c r="A16" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" hidden="1" outlineLevel="2">
+      <c r="A17" s="4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" hidden="1" outlineLevel="2">
+      <c r="A19" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" hidden="1" outlineLevel="2">
+      <c r="A20" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" hidden="1" outlineLevel="2">
+      <c r="A21" s="4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" collapsed="1">
+      <c r="A22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>intro+verse 1</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progBlingBlingColoring(33090, 10, 5000)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_GLOW, Farben SCHEME_ROYAL, Farbwanderung to triad, per 8
+Ausgabe: Helligkeit 60 %
+'in the dark': die Geräte füllen sich langsam in Blau und Lila, gedimmt auf 60 %; die Farben wandern alle 2 Takte nach Pink/Orange und zurück.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>16 Takte ein Effekt sind lang. Szene Glow, ROYAL, Farbwanderung (triad, 2 Takte), auf 60 % gedimmt - "in the dark".
 Besser: bei Takt 13 eine eigene Zeile "verse 1" anlegen - dann ab dort Szene Verse (Puls im Beat).</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5">
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(33090, 10, 5000)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+    <row r="23" hidden="1" outlineLevel="2">
+      <c r="A23" s="4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24" hidden="1" outlineLevel="2">
+      <c r="A24" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25" hidden="1" outlineLevel="2">
+      <c r="A25" s="4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27" hidden="1" outlineLevel="2">
+      <c r="A27" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28" hidden="1" outlineLevel="2">
+      <c r="A28" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29" hidden="1" outlineLevel="2">
+      <c r="A29" s="4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="31" hidden="1" outlineLevel="2">
+      <c r="A31" s="4" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="6" t="n"/>
+    </row>
+    <row r="32" hidden="1" outlineLevel="2">
+      <c r="A32" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="6" t="n"/>
+    </row>
+    <row r="33" hidden="1" outlineLevel="2">
+      <c r="A33" s="4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="6" t="n"/>
+    </row>
+    <row r="35" hidden="1" outlineLevel="2">
+      <c r="A35" s="4" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="6" t="n"/>
+    </row>
+    <row r="36" hidden="1" outlineLevel="2">
+      <c r="A36" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37" hidden="1" outlineLevel="2">
+      <c r="A37" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="6" t="n"/>
+    </row>
+    <row r="38" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A38" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="6" t="n"/>
+    </row>
+    <row r="39" hidden="1" outlineLevel="2">
+      <c r="A39" s="4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="6" t="n"/>
+    </row>
+    <row r="40" hidden="1" outlineLevel="2">
+      <c r="A40" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="6" t="n"/>
+    </row>
+    <row r="41" hidden="1" outlineLevel="2">
+      <c r="A41" s="4" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="6" t="n"/>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="6" t="n"/>
+    </row>
+    <row r="43" hidden="1" outlineLevel="2">
+      <c r="A43" s="4" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="6" t="n"/>
+    </row>
+    <row r="44" hidden="1" outlineLevel="2">
+      <c r="A44" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="6" t="n"/>
+    </row>
+    <row r="45" hidden="1" outlineLevel="2">
+      <c r="A45" s="4" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="6" t="n"/>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A46" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="6" t="n"/>
+    </row>
+    <row r="47" hidden="1" outlineLevel="2">
+      <c r="A47" s="4" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="6" t="n"/>
+    </row>
+    <row r="48" hidden="1" outlineLevel="2">
+      <c r="A48" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="6" t="n"/>
+    </row>
+    <row r="49" hidden="1" outlineLevel="2">
+      <c r="A49" s="4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="51" hidden="1" outlineLevel="2">
+      <c r="A51" s="4" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="6" t="n"/>
+    </row>
+    <row r="52" hidden="1" outlineLevel="2">
+      <c r="A52" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="6" t="n"/>
+    </row>
+    <row r="53" hidden="1" outlineLevel="2">
+      <c r="A53" s="4" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="6" t="n"/>
+    </row>
+    <row r="54" collapsed="1">
+      <c r="A54" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>verse 1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_ROYAL
+Strophe: dezenter Puls im Beat in Blau und Lila, auf der Matrix Plasma-Wolken.</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="6" t="n"/>
+    </row>
+    <row r="55" hidden="1" outlineLevel="2">
+      <c r="A55" s="4" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="6" t="n"/>
+    </row>
+    <row r="56" hidden="1" outlineLevel="2">
+      <c r="A56" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="6" t="n"/>
+    </row>
+    <row r="57" hidden="1" outlineLevel="2">
+      <c r="A57" s="4" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="6" t="n"/>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="6" t="n"/>
+    </row>
+    <row r="59" hidden="1" outlineLevel="2">
+      <c r="A59" s="4" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="6" t="n"/>
+    </row>
+    <row r="60" hidden="1" outlineLevel="2">
+      <c r="A60" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="6" t="n"/>
+    </row>
+    <row r="61" hidden="1" outlineLevel="2">
+      <c r="A61" s="4" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="6" t="n"/>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="6" t="n"/>
+    </row>
+    <row r="63" hidden="1" outlineLevel="2">
+      <c r="A63" s="4" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="6" t="n"/>
+    </row>
+    <row r="64" hidden="1" outlineLevel="2">
+      <c r="A64" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="6" t="n"/>
+    </row>
+    <row r="65" hidden="1" outlineLevel="2">
+      <c r="A65" s="4" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="6" t="n"/>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A66" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="6" t="n"/>
+    </row>
+    <row r="67" hidden="1" outlineLevel="2">
+      <c r="A67" s="4" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="6" t="n"/>
+    </row>
+    <row r="68" hidden="1" outlineLevel="2">
+      <c r="A68" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="6" t="n"/>
+    </row>
+    <row r="69" hidden="1" outlineLevel="2">
+      <c r="A69" s="4" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="6" t="n"/>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A70" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="6" t="n"/>
+    </row>
+    <row r="71" hidden="1" outlineLevel="2">
+      <c r="A71" s="4" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="6" t="n"/>
+    </row>
+    <row r="72" hidden="1" outlineLevel="2">
+      <c r="A72" s="4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="6" t="n"/>
+    </row>
+    <row r="73" hidden="1" outlineLevel="2">
+      <c r="A73" s="4" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="6" t="n"/>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A74" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="6" t="n"/>
+    </row>
+    <row r="75" hidden="1" outlineLevel="2">
+      <c r="A75" s="4" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="6" t="n"/>
+    </row>
+    <row r="76" hidden="1" outlineLevel="2">
+      <c r="A76" s="4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="6" t="n"/>
+    </row>
+    <row r="77" hidden="1" outlineLevel="2">
+      <c r="A77" s="4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="6" t="n"/>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A78" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="6" t="n"/>
+    </row>
+    <row r="79" hidden="1" outlineLevel="2">
+      <c r="A79" s="4" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="6" t="n"/>
+    </row>
+    <row r="80" hidden="1" outlineLevel="2">
+      <c r="A80" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="6" t="n"/>
+    </row>
+    <row r="81" hidden="1" outlineLevel="2">
+      <c r="A81" s="4" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="6" t="n"/>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A82" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="6" t="n"/>
+    </row>
+    <row r="83" hidden="1" outlineLevel="2">
+      <c r="A83" s="4" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="6" t="n"/>
+    </row>
+    <row r="84" hidden="1" outlineLevel="2">
+      <c r="A84" s="4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="6" t="n"/>
+    </row>
+    <row r="85" hidden="1" outlineLevel="2">
+      <c r="A85" s="4" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="6" t="n"/>
+    </row>
+    <row r="86" collapsed="1">
+      <c r="A86" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>bridge 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFullColors(16550, 12, 515)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS_WAVE, Farben SCHEME_SUNSET
+Ausgabe: Farbwechsel weich (60 % des Schritts)
+Schluss (4 Beats): SCENE_COLORS, Farben SCHEME_WHITE
+   Ausgabe: Tor 4x pro Beat, 50 % hell
+Die Farbe wandert pro Beat weich von Gerät zu Gerät, in Orange, Pink, Lila und Gelb; im letzten Takt weißer Strobo im Takt (4 Blitze pro Beat).</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>Szene Colors Wave, SUNSET, soft 60: die Farbe wandert pro Beat weich von Gerät zu Gerät. Letzter Takt weißer Strobo (tail 4 Beats).</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5">
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>progFullColors(16550, 12, 515)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="87" hidden="1" outlineLevel="2">
+      <c r="A87" s="4" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="6" t="n"/>
+    </row>
+    <row r="88" hidden="1" outlineLevel="2">
+      <c r="A88" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="6" t="n"/>
+    </row>
+    <row r="89" hidden="1" outlineLevel="2">
+      <c r="A89" s="4" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="6" t="n"/>
+    </row>
+    <row r="90" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A90" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="6" t="n"/>
+    </row>
+    <row r="91" hidden="1" outlineLevel="2">
+      <c r="A91" s="4" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="6" t="n"/>
+    </row>
+    <row r="92" hidden="1" outlineLevel="2">
+      <c r="A92" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="6" t="n"/>
+    </row>
+    <row r="93" hidden="1" outlineLevel="2">
+      <c r="A93" s="4" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="6" t="n"/>
+    </row>
+    <row r="94" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A94" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="6" t="n"/>
+    </row>
+    <row r="95" hidden="1" outlineLevel="2">
+      <c r="A95" s="4" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="6" t="n"/>
+    </row>
+    <row r="96" hidden="1" outlineLevel="2">
+      <c r="A96" s="4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="6" t="n"/>
+    </row>
+    <row r="97" hidden="1" outlineLevel="2">
+      <c r="A97" s="4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="6" t="n"/>
+    </row>
+    <row r="98" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A98" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="6" t="n"/>
+    </row>
+    <row r="99" hidden="1" outlineLevel="2">
+      <c r="A99" s="4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="6" t="n"/>
+    </row>
+    <row r="100" hidden="1" outlineLevel="2">
+      <c r="A100" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="6" t="n"/>
+    </row>
+    <row r="101" hidden="1" outlineLevel="2">
+      <c r="A101" s="4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="6" t="n"/>
+    </row>
+    <row r="102" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A102" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="6" t="n"/>
+    </row>
+    <row r="103" hidden="1" outlineLevel="2">
+      <c r="A103" s="4" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="6" t="n"/>
+    </row>
+    <row r="104" hidden="1" outlineLevel="2">
+      <c r="A104" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="6" t="n"/>
+    </row>
+    <row r="105" hidden="1" outlineLevel="2">
+      <c r="A105" s="4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="6" t="n"/>
+    </row>
+    <row r="106" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A106" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="6" t="n"/>
+    </row>
+    <row r="107" hidden="1" outlineLevel="2">
+      <c r="A107" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="6" t="n"/>
+    </row>
+    <row r="108" hidden="1" outlineLevel="2">
+      <c r="A108" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="6" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="6" t="n"/>
+    </row>
+    <row r="109" hidden="1" outlineLevel="2">
+      <c r="A109" s="4" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="6" t="n"/>
+    </row>
+    <row r="110" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A110" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="6" t="n"/>
+    </row>
+    <row r="111" hidden="1" outlineLevel="2">
+      <c r="A111" s="4" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+      <c r="E111" s="6" t="n"/>
+      <c r="F111" s="5" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="6" t="n"/>
+    </row>
+    <row r="112" hidden="1" outlineLevel="2">
+      <c r="A112" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="6" t="n"/>
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="6" t="n"/>
+    </row>
+    <row r="113" hidden="1" outlineLevel="2">
+      <c r="A113" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="B113" s="5" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="6" t="n"/>
+    </row>
+    <row r="114" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A114" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="6" t="n"/>
+    </row>
+    <row r="115" hidden="1" outlineLevel="2">
+      <c r="A115" s="4" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="6" t="n"/>
+      <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="6" t="n"/>
+    </row>
+    <row r="116" hidden="1" outlineLevel="2">
+      <c r="A116" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="5" t="n"/>
+      <c r="G116" s="5" t="n"/>
+      <c r="H116" s="6" t="n"/>
+    </row>
+    <row r="117" hidden="1" outlineLevel="2">
+      <c r="A117" s="4" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="6" t="n"/>
+      <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="6" t="n"/>
+    </row>
+    <row r="118" collapsed="1">
+      <c r="A118" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progSternNeu(16550, 1035, 14, 5, 26, 5, true, 3)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_NEON
+Ausgabe: Blinder bei 0 ms, 1034 ms lang
+Der Chorus springt aus dem Dunkel: drehender Stern in Pink, Cyan und Violett, warmweißer Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>Szene Star, NEON, Blinder auf den Einsatz (2 Beats).</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5">
+      <c r="F118" s="5" t="n"/>
+      <c r="G118" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H118" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 1035, 14, 5, 26, 5, true, 3)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+    <row r="119" hidden="1" outlineLevel="2">
+      <c r="A119" s="4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+      <c r="E119" s="6" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="6" t="n"/>
+    </row>
+    <row r="120" hidden="1" outlineLevel="2">
+      <c r="A120" s="4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="6" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="6" t="n"/>
+    </row>
+    <row r="121" hidden="1" outlineLevel="2">
+      <c r="A121" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="F121" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="6" t="n"/>
+    </row>
+    <row r="122" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A122" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="6" t="n"/>
+      <c r="F122" s="5" t="n"/>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="6" t="n"/>
+    </row>
+    <row r="123" hidden="1" outlineLevel="2">
+      <c r="A123" s="4" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="6" t="n"/>
+      <c r="E123" s="6" t="n"/>
+      <c r="F123" s="5" t="n"/>
+      <c r="G123" s="5" t="n"/>
+      <c r="H123" s="6" t="n"/>
+    </row>
+    <row r="124" hidden="1" outlineLevel="2">
+      <c r="A124" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="6" t="n"/>
+      <c r="D124" s="6" t="n"/>
+      <c r="E124" s="6" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="6" t="n"/>
+    </row>
+    <row r="125" hidden="1" outlineLevel="2">
+      <c r="A125" s="4" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="E125" s="6" t="n"/>
+      <c r="F125" s="5" t="n"/>
+      <c r="G125" s="5" t="n"/>
+      <c r="H125" s="6" t="n"/>
+    </row>
+    <row r="126" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A126" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B126" s="5" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+      <c r="E126" s="6" t="n"/>
+      <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="6" t="n"/>
+    </row>
+    <row r="127" hidden="1" outlineLevel="2">
+      <c r="A127" s="4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="6" t="n"/>
+      <c r="E127" s="6" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="6" t="n"/>
+    </row>
+    <row r="128" hidden="1" outlineLevel="2">
+      <c r="A128" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="6" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="6" t="n"/>
+    </row>
+    <row r="129" hidden="1" outlineLevel="2">
+      <c r="A129" s="4" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="6" t="n"/>
+      <c r="E129" s="6" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="6" t="n"/>
+    </row>
+    <row r="130" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A130" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="6" t="n"/>
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="6" t="n"/>
+    </row>
+    <row r="131" hidden="1" outlineLevel="2">
+      <c r="A131" s="4" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="6" t="n"/>
+      <c r="E131" s="6" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="6" t="n"/>
+    </row>
+    <row r="132" hidden="1" outlineLevel="2">
+      <c r="A132" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="6" t="n"/>
+      <c r="E132" s="6" t="n"/>
+      <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="6" t="n"/>
+    </row>
+    <row r="133" hidden="1" outlineLevel="2">
+      <c r="A133" s="4" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="B133" s="5" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+      <c r="E133" s="6" t="n"/>
+      <c r="F133" s="5" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="6" t="n"/>
+    </row>
+    <row r="134" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A134" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B134" s="5" t="n"/>
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="6" t="n"/>
+      <c r="E134" s="6" t="n"/>
+      <c r="F134" s="5" t="n"/>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="6" t="n"/>
+    </row>
+    <row r="135" hidden="1" outlineLevel="2">
+      <c r="A135" s="4" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+      <c r="E135" s="6" t="n"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="6" t="n"/>
+    </row>
+    <row r="136" hidden="1" outlineLevel="2">
+      <c r="A136" s="4" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="6" t="n"/>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="6" t="n"/>
+    </row>
+    <row r="137" hidden="1" outlineLevel="2">
+      <c r="A137" s="4" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+      <c r="E137" s="6" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="6" t="n"/>
+    </row>
+    <row r="138" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A138" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B138" s="5" t="n"/>
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="6" t="n"/>
+      <c r="E138" s="6" t="n"/>
+      <c r="F138" s="5" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="6" t="n"/>
+    </row>
+    <row r="139" hidden="1" outlineLevel="2">
+      <c r="A139" s="4" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+      <c r="E139" s="6" t="n"/>
+      <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
+      <c r="H139" s="6" t="n"/>
+    </row>
+    <row r="140" hidden="1" outlineLevel="2">
+      <c r="A140" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="6" t="n"/>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="6" t="n"/>
+    </row>
+    <row r="141" hidden="1" outlineLevel="2">
+      <c r="A141" s="4" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+      <c r="E141" s="6" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="6" t="n"/>
+    </row>
+    <row r="142" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A142" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="n"/>
+      <c r="E142" s="6" t="n"/>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="6" t="n"/>
+    </row>
+    <row r="143" hidden="1" outlineLevel="2">
+      <c r="A143" s="4" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+      <c r="E143" s="6" t="n"/>
+      <c r="F143" s="5" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="6" t="n"/>
+    </row>
+    <row r="144" hidden="1" outlineLevel="2">
+      <c r="A144" s="4" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="6" t="n"/>
+    </row>
+    <row r="145" hidden="1" outlineLevel="2">
+      <c r="A145" s="4" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="6" t="n"/>
+      <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
+      <c r="H145" s="6" t="n"/>
+    </row>
+    <row r="146" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A146" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="6" t="n"/>
+      <c r="D146" s="6" t="n"/>
+      <c r="E146" s="6" t="n"/>
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="6" t="n"/>
+    </row>
+    <row r="147" hidden="1" outlineLevel="2">
+      <c r="A147" s="4" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="6" t="n"/>
+      <c r="E147" s="6" t="n"/>
+      <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
+      <c r="H147" s="6" t="n"/>
+    </row>
+    <row r="148" hidden="1" outlineLevel="2">
+      <c r="A148" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="6" t="n"/>
+      <c r="D148" s="6" t="n"/>
+      <c r="E148" s="6" t="n"/>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="6" t="n"/>
+    </row>
+    <row r="149" hidden="1" outlineLevel="2">
+      <c r="A149" s="4" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
+      <c r="H149" s="6" t="n"/>
+    </row>
+    <row r="150" collapsed="1">
+      <c r="A150" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progPalette(16540, 4, 16)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_DNA_FLIP_SCROLL, Farben SCHEME_ROYAL
+Ausgabe: Übergang fade 1034 ms
+Weich eingeblendet: eine DNA-Helix in Blau und Lila wandert langsam über die Matrix, die Stränge tauschen jeden Takt die Seiten; alle anderen Geräte pulsieren einmal je Takt.</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="n"/>
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>Szene DNA Flip Scroll, ROYAL: Helix auf der Matrix, alle anderen pulsieren einmal je Takt. Weich eingeblendet (fade, 2 Beats).</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5">
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H150" s="6" t="inlineStr">
         <is>
           <t>progPalette(16540, 4, 16)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="151" hidden="1" outlineLevel="2">
+      <c r="A151" s="4" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+      <c r="E151" s="6" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="6" t="n"/>
+    </row>
+    <row r="152" hidden="1" outlineLevel="2">
+      <c r="A152" s="4" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="6" t="n"/>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="6" t="n"/>
+    </row>
+    <row r="153" hidden="1" outlineLevel="2">
+      <c r="A153" s="4" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="6" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="6" t="n"/>
+    </row>
+    <row r="154" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A154" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B154" s="5" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="5" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="6" t="n"/>
+    </row>
+    <row r="155" hidden="1" outlineLevel="2">
+      <c r="A155" s="4" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+      <c r="E155" s="6" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="6" t="n"/>
+    </row>
+    <row r="156" hidden="1" outlineLevel="2">
+      <c r="A156" s="4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="n"/>
+      <c r="E156" s="6" t="n"/>
+      <c r="F156" s="5" t="n"/>
+      <c r="G156" s="5" t="n"/>
+      <c r="H156" s="6" t="n"/>
+    </row>
+    <row r="157" hidden="1" outlineLevel="2">
+      <c r="A157" s="4" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="F157" s="5" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="6" t="n"/>
+    </row>
+    <row r="158" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A158" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B158" s="5" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+      <c r="E158" s="6" t="n"/>
+      <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
+      <c r="H158" s="6" t="n"/>
+    </row>
+    <row r="159" hidden="1" outlineLevel="2">
+      <c r="A159" s="4" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="6" t="n"/>
+      <c r="E159" s="6" t="n"/>
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="6" t="n"/>
+    </row>
+    <row r="160" hidden="1" outlineLevel="2">
+      <c r="A160" s="4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+      <c r="E160" s="6" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="6" t="n"/>
+    </row>
+    <row r="161" hidden="1" outlineLevel="2">
+      <c r="A161" s="4" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="6" t="n"/>
+      <c r="E161" s="6" t="n"/>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="6" t="n"/>
+    </row>
+    <row r="162" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A162" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="6" t="n"/>
+      <c r="E162" s="6" t="n"/>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="6" t="n"/>
+    </row>
+    <row r="163" hidden="1" outlineLevel="2">
+      <c r="A163" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="6" t="n"/>
+      <c r="E163" s="6" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="6" t="n"/>
+    </row>
+    <row r="164" hidden="1" outlineLevel="2">
+      <c r="A164" s="4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="6" t="n"/>
+      <c r="D164" s="6" t="n"/>
+      <c r="E164" s="6" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="6" t="n"/>
+    </row>
+    <row r="165" hidden="1" outlineLevel="2">
+      <c r="A165" s="4" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="6" t="n"/>
+      <c r="E165" s="6" t="n"/>
+      <c r="F165" s="5" t="n"/>
+      <c r="G165" s="5" t="n"/>
+      <c r="H165" s="6" t="n"/>
+    </row>
+    <row r="166" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A166" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="6" t="n"/>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="6" t="n"/>
+    </row>
+    <row r="167" hidden="1" outlineLevel="2">
+      <c r="A167" s="4" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="6" t="n"/>
+      <c r="D167" s="6" t="n"/>
+      <c r="E167" s="6" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="6" t="n"/>
+    </row>
+    <row r="168" hidden="1" outlineLevel="2">
+      <c r="A168" s="4" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="6" t="n"/>
+      <c r="E168" s="6" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="6" t="n"/>
+    </row>
+    <row r="169" hidden="1" outlineLevel="2">
+      <c r="A169" s="4" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+      <c r="E169" s="6" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="6" t="n"/>
+    </row>
+    <row r="170" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A170" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+      <c r="E170" s="6" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="6" t="n"/>
+    </row>
+    <row r="171" hidden="1" outlineLevel="2">
+      <c r="A171" s="4" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="6" t="n"/>
+      <c r="D171" s="6" t="n"/>
+      <c r="E171" s="6" t="n"/>
+      <c r="F171" s="5" t="n"/>
+      <c r="G171" s="5" t="n"/>
+      <c r="H171" s="6" t="n"/>
+    </row>
+    <row r="172" hidden="1" outlineLevel="2">
+      <c r="A172" s="4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+      <c r="E172" s="6" t="n"/>
+      <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
+      <c r="H172" s="6" t="n"/>
+    </row>
+    <row r="173" hidden="1" outlineLevel="2">
+      <c r="A173" s="4" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+      <c r="E173" s="6" t="n"/>
+      <c r="F173" s="5" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="6" t="n"/>
+    </row>
+    <row r="174" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A174" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="6" t="n"/>
+      <c r="D174" s="6" t="n"/>
+      <c r="E174" s="6" t="n"/>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="6" t="n"/>
+    </row>
+    <row r="175" hidden="1" outlineLevel="2">
+      <c r="A175" s="4" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="6" t="n"/>
+      <c r="D175" s="6" t="n"/>
+      <c r="E175" s="6" t="n"/>
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="6" t="n"/>
+    </row>
+    <row r="176" hidden="1" outlineLevel="2">
+      <c r="A176" s="4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="6" t="n"/>
+      <c r="D176" s="6" t="n"/>
+      <c r="E176" s="6" t="n"/>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="6" t="n"/>
+    </row>
+    <row r="177" hidden="1" outlineLevel="2">
+      <c r="A177" s="4" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+      <c r="E177" s="6" t="n"/>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="6" t="n"/>
+    </row>
+    <row r="178" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A178" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="6" t="n"/>
+      <c r="D178" s="6" t="n"/>
+      <c r="E178" s="6" t="n"/>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
+      <c r="H178" s="6" t="n"/>
+    </row>
+    <row r="179" hidden="1" outlineLevel="2">
+      <c r="A179" s="4" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="6" t="n"/>
+      <c r="D179" s="6" t="n"/>
+      <c r="E179" s="6" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="6" t="n"/>
+    </row>
+    <row r="180" hidden="1" outlineLevel="2">
+      <c r="A180" s="4" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="6" t="n"/>
+      <c r="D180" s="6" t="n"/>
+      <c r="E180" s="6" t="n"/>
+      <c r="F180" s="5" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="6" t="n"/>
+    </row>
+    <row r="181" hidden="1" outlineLevel="2">
+      <c r="A181" s="4" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+      <c r="E181" s="6" t="n"/>
+      <c r="F181" s="5" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="6" t="n"/>
+    </row>
+    <row r="182" collapsed="1">
+      <c r="A182" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>bridge 2</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progRandomLines(16550, 18, 515, true)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_CALL_RESPONSE, Farben SCHEME_SUNSET
+Schluss (4 Beats): SCENE_COLORS, Farben SCHEME_WHITE
+   Ausgabe: Tor 4x pro Beat, 50 % hell
+Die Bühnenhälften blitzen abwechselnd im Beat in warmen Farben; im letzten Takt weißer Strobo im Takt.</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="n"/>
+      <c r="E182" s="6" t="inlineStr">
         <is>
           <t>Szene Call Response, SUNSET: Bühnenhälften blitzen abwechselnd im Beat. Letzter Takt weißer Strobo (tail 4 Beats).</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5">
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H182" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16550, 18, 515, true)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+    <row r="183" hidden="1" outlineLevel="2">
+      <c r="A183" s="4" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+      <c r="E183" s="6" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="6" t="n"/>
+    </row>
+    <row r="184" hidden="1" outlineLevel="2">
+      <c r="A184" s="4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="F184" s="5" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="6" t="n"/>
+    </row>
+    <row r="185" hidden="1" outlineLevel="2">
+      <c r="A185" s="4" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+      <c r="E185" s="6" t="n"/>
+      <c r="F185" s="5" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="6" t="n"/>
+    </row>
+    <row r="186" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A186" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="n"/>
+      <c r="E186" s="6" t="n"/>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="6" t="n"/>
+    </row>
+    <row r="187" hidden="1" outlineLevel="2">
+      <c r="A187" s="4" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="6" t="n"/>
+      <c r="D187" s="6" t="n"/>
+      <c r="E187" s="6" t="n"/>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="6" t="n"/>
+    </row>
+    <row r="188" hidden="1" outlineLevel="2">
+      <c r="A188" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="6" t="n"/>
+      <c r="D188" s="6" t="n"/>
+      <c r="E188" s="6" t="n"/>
+      <c r="F188" s="5" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="6" t="n"/>
+    </row>
+    <row r="189" hidden="1" outlineLevel="2">
+      <c r="A189" s="4" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="6" t="n"/>
+      <c r="D189" s="6" t="n"/>
+      <c r="E189" s="6" t="n"/>
+      <c r="F189" s="5" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="6" t="n"/>
+    </row>
+    <row r="190" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A190" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+      <c r="E190" s="6" t="n"/>
+      <c r="F190" s="5" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="6" t="n"/>
+    </row>
+    <row r="191" hidden="1" outlineLevel="2">
+      <c r="A191" s="4" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="6" t="n"/>
+      <c r="D191" s="6" t="n"/>
+      <c r="E191" s="6" t="n"/>
+      <c r="F191" s="5" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="6" t="n"/>
+    </row>
+    <row r="192" hidden="1" outlineLevel="2">
+      <c r="A192" s="4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="6" t="n"/>
+      <c r="D192" s="6" t="n"/>
+      <c r="E192" s="6" t="n"/>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="6" t="n"/>
+    </row>
+    <row r="193" hidden="1" outlineLevel="2">
+      <c r="A193" s="4" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+      <c r="E193" s="6" t="n"/>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="6" t="n"/>
+    </row>
+    <row r="194" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A194" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="6" t="n"/>
+      <c r="D194" s="6" t="n"/>
+      <c r="E194" s="6" t="n"/>
+      <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5" t="n"/>
+      <c r="H194" s="6" t="n"/>
+    </row>
+    <row r="195" hidden="1" outlineLevel="2">
+      <c r="A195" s="4" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="6" t="n"/>
+      <c r="D195" s="6" t="n"/>
+      <c r="E195" s="6" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="6" t="n"/>
+    </row>
+    <row r="196" hidden="1" outlineLevel="2">
+      <c r="A196" s="4" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="6" t="n"/>
+      <c r="D196" s="6" t="n"/>
+      <c r="E196" s="6" t="n"/>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="6" t="n"/>
+    </row>
+    <row r="197" hidden="1" outlineLevel="2">
+      <c r="A197" s="4" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="6" t="n"/>
+      <c r="D197" s="6" t="n"/>
+      <c r="E197" s="6" t="n"/>
+      <c r="F197" s="5" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="6" t="n"/>
+    </row>
+    <row r="198" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A198" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+      <c r="E198" s="6" t="n"/>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="6" t="n"/>
+    </row>
+    <row r="199" hidden="1" outlineLevel="2">
+      <c r="A199" s="4" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="6" t="n"/>
+      <c r="D199" s="6" t="n"/>
+      <c r="E199" s="6" t="n"/>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="6" t="n"/>
+    </row>
+    <row r="200" hidden="1" outlineLevel="2">
+      <c r="A200" s="4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+      <c r="E200" s="6" t="n"/>
+      <c r="F200" s="5" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="6" t="n"/>
+    </row>
+    <row r="201" hidden="1" outlineLevel="2">
+      <c r="A201" s="4" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="6" t="n"/>
+      <c r="D201" s="6" t="n"/>
+      <c r="E201" s="6" t="n"/>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="6" t="n"/>
+    </row>
+    <row r="202" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A202" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="6" t="n"/>
+      <c r="D202" s="6" t="n"/>
+      <c r="E202" s="6" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="6" t="n"/>
+    </row>
+    <row r="203" hidden="1" outlineLevel="2">
+      <c r="A203" s="4" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="B203" s="5" t="n"/>
+      <c r="C203" s="6" t="n"/>
+      <c r="D203" s="6" t="n"/>
+      <c r="E203" s="6" t="n"/>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="6" t="n"/>
+    </row>
+    <row r="204" hidden="1" outlineLevel="2">
+      <c r="A204" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="6" t="n"/>
+      <c r="D204" s="6" t="n"/>
+      <c r="E204" s="6" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="6" t="n"/>
+    </row>
+    <row r="205" hidden="1" outlineLevel="2">
+      <c r="A205" s="4" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="6" t="n"/>
+      <c r="D205" s="6" t="n"/>
+      <c r="E205" s="6" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="6" t="n"/>
+    </row>
+    <row r="206" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A206" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="6" t="n"/>
+      <c r="D206" s="6" t="n"/>
+      <c r="E206" s="6" t="n"/>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="6" t="n"/>
+    </row>
+    <row r="207" hidden="1" outlineLevel="2">
+      <c r="A207" s="4" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="6" t="n"/>
+      <c r="D207" s="6" t="n"/>
+      <c r="E207" s="6" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="6" t="n"/>
+    </row>
+    <row r="208" hidden="1" outlineLevel="2">
+      <c r="A208" s="4" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="6" t="n"/>
+      <c r="D208" s="6" t="n"/>
+      <c r="E208" s="6" t="n"/>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="6" t="n"/>
+    </row>
+    <row r="209" hidden="1" outlineLevel="2">
+      <c r="A209" s="4" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="6" t="n"/>
+      <c r="D209" s="6" t="n"/>
+      <c r="E209" s="6" t="n"/>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="6" t="n"/>
+    </row>
+    <row r="210" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A210" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="n"/>
+      <c r="E210" s="6" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="6" t="n"/>
+    </row>
+    <row r="211" hidden="1" outlineLevel="2">
+      <c r="A211" s="4" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="6" t="n"/>
+      <c r="D211" s="6" t="n"/>
+      <c r="E211" s="6" t="n"/>
+      <c r="F211" s="5" t="n"/>
+      <c r="G211" s="5" t="n"/>
+      <c r="H211" s="6" t="n"/>
+    </row>
+    <row r="212" hidden="1" outlineLevel="2">
+      <c r="A212" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="6" t="n"/>
+      <c r="D212" s="6" t="n"/>
+      <c r="E212" s="6" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="6" t="n"/>
+    </row>
+    <row r="213" hidden="1" outlineLevel="2">
+      <c r="A213" s="4" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="6" t="n"/>
+      <c r="D213" s="6" t="n"/>
+      <c r="E213" s="6" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="6" t="n"/>
+    </row>
+    <row r="214" collapsed="1">
+      <c r="A214" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B214" s="5" t="inlineStr">
         <is>
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progSternNeu(16550, 1035, 20, 5, 26, 5, false, 4)
-! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = 0</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_NEON
+Ausgabe: Blinder bei 0 ms, 1034 ms lang, Blinder alle 2 Beat(s), 259 ms, nur LAMPE1, LAMPE2
+Stern in Pink, Cyan und Violett wie in chorus 1 mit Blinder auf den Einsatz; dazu blitzen die Lampen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="n"/>
+      <c r="E214" s="6" t="inlineStr">
         <is>
           <t>Szene Star, NEON wie chorus 1, dazu blitzen die Lampen weiß auf 2 und 4.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5">
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 1035, 20, 5, 26, 5, false, 4)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = 0</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="215" hidden="1" outlineLevel="2">
+      <c r="A215" s="4" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="6" t="n"/>
+      <c r="D215" s="6" t="n"/>
+      <c r="E215" s="6" t="n"/>
+      <c r="F215" s="5" t="n"/>
+      <c r="G215" s="5" t="n"/>
+      <c r="H215" s="6" t="n"/>
+    </row>
+    <row r="216" hidden="1" outlineLevel="2">
+      <c r="A216" s="4" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="6" t="n"/>
+      <c r="D216" s="6" t="n"/>
+      <c r="E216" s="6" t="n"/>
+      <c r="F216" s="5" t="n"/>
+      <c r="G216" s="5" t="n"/>
+      <c r="H216" s="6" t="n"/>
+    </row>
+    <row r="217" hidden="1" outlineLevel="2">
+      <c r="A217" s="4" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="6" t="n"/>
+      <c r="D217" s="6" t="n"/>
+      <c r="E217" s="6" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="6" t="n"/>
+    </row>
+    <row r="218" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A218" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="6" t="n"/>
+      <c r="D218" s="6" t="n"/>
+      <c r="E218" s="6" t="n"/>
+      <c r="F218" s="5" t="n"/>
+      <c r="G218" s="5" t="n"/>
+      <c r="H218" s="6" t="n"/>
+    </row>
+    <row r="219" hidden="1" outlineLevel="2">
+      <c r="A219" s="4" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="6" t="n"/>
+      <c r="D219" s="6" t="n"/>
+      <c r="E219" s="6" t="n"/>
+      <c r="F219" s="5" t="n"/>
+      <c r="G219" s="5" t="n"/>
+      <c r="H219" s="6" t="n"/>
+    </row>
+    <row r="220" hidden="1" outlineLevel="2">
+      <c r="A220" s="4" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="6" t="n"/>
+      <c r="D220" s="6" t="n"/>
+      <c r="E220" s="6" t="n"/>
+      <c r="F220" s="5" t="n"/>
+      <c r="G220" s="5" t="n"/>
+      <c r="H220" s="6" t="n"/>
+    </row>
+    <row r="221" hidden="1" outlineLevel="2">
+      <c r="A221" s="4" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="6" t="n"/>
+      <c r="D221" s="6" t="n"/>
+      <c r="E221" s="6" t="n"/>
+      <c r="F221" s="5" t="n"/>
+      <c r="G221" s="5" t="n"/>
+      <c r="H221" s="6" t="n"/>
+    </row>
+    <row r="222" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A222" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="6" t="n"/>
+      <c r="D222" s="6" t="n"/>
+      <c r="E222" s="6" t="n"/>
+      <c r="F222" s="5" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="6" t="n"/>
+    </row>
+    <row r="223" hidden="1" outlineLevel="2">
+      <c r="A223" s="4" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="6" t="n"/>
+      <c r="D223" s="6" t="n"/>
+      <c r="E223" s="6" t="n"/>
+      <c r="F223" s="5" t="n"/>
+      <c r="G223" s="5" t="n"/>
+      <c r="H223" s="6" t="n"/>
+    </row>
+    <row r="224" hidden="1" outlineLevel="2">
+      <c r="A224" s="4" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="B224" s="5" t="n"/>
+      <c r="C224" s="6" t="n"/>
+      <c r="D224" s="6" t="n"/>
+      <c r="E224" s="6" t="n"/>
+      <c r="F224" s="5" t="n"/>
+      <c r="G224" s="5" t="n"/>
+      <c r="H224" s="6" t="n"/>
+    </row>
+    <row r="225" hidden="1" outlineLevel="2">
+      <c r="A225" s="4" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="6" t="n"/>
+      <c r="D225" s="6" t="n"/>
+      <c r="E225" s="6" t="n"/>
+      <c r="F225" s="5" t="n"/>
+      <c r="G225" s="5" t="n"/>
+      <c r="H225" s="6" t="n"/>
+    </row>
+    <row r="226" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A226" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="6" t="n"/>
+      <c r="D226" s="6" t="n"/>
+      <c r="E226" s="6" t="n"/>
+      <c r="F226" s="5" t="n"/>
+      <c r="G226" s="5" t="n"/>
+      <c r="H226" s="6" t="n"/>
+    </row>
+    <row r="227" hidden="1" outlineLevel="2">
+      <c r="A227" s="4" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+      <c r="E227" s="6" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="6" t="n"/>
+    </row>
+    <row r="228" hidden="1" outlineLevel="2">
+      <c r="A228" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="6" t="n"/>
+      <c r="D228" s="6" t="n"/>
+      <c r="E228" s="6" t="n"/>
+      <c r="F228" s="5" t="n"/>
+      <c r="G228" s="5" t="n"/>
+      <c r="H228" s="6" t="n"/>
+    </row>
+    <row r="229" hidden="1" outlineLevel="2">
+      <c r="A229" s="4" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="6" t="n"/>
+      <c r="D229" s="6" t="n"/>
+      <c r="E229" s="6" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="6" t="n"/>
+    </row>
+    <row r="230" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A230" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="6" t="n"/>
+      <c r="D230" s="6" t="n"/>
+      <c r="E230" s="6" t="n"/>
+      <c r="F230" s="5" t="n"/>
+      <c r="G230" s="5" t="n"/>
+      <c r="H230" s="6" t="n"/>
+    </row>
+    <row r="231" hidden="1" outlineLevel="2">
+      <c r="A231" s="4" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="6" t="n"/>
+      <c r="D231" s="6" t="n"/>
+      <c r="E231" s="6" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="6" t="n"/>
+    </row>
+    <row r="232" hidden="1" outlineLevel="2">
+      <c r="A232" s="4" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="6" t="n"/>
+      <c r="D232" s="6" t="n"/>
+      <c r="E232" s="6" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="6" t="n"/>
+    </row>
+    <row r="233" hidden="1" outlineLevel="2">
+      <c r="A233" s="4" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="6" t="n"/>
+      <c r="D233" s="6" t="n"/>
+      <c r="E233" s="6" t="n"/>
+      <c r="F233" s="5" t="n"/>
+      <c r="G233" s="5" t="n"/>
+      <c r="H233" s="6" t="n"/>
+    </row>
+    <row r="234" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A234" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="6" t="n"/>
+      <c r="D234" s="6" t="n"/>
+      <c r="E234" s="6" t="n"/>
+      <c r="F234" s="5" t="n"/>
+      <c r="G234" s="5" t="n"/>
+      <c r="H234" s="6" t="n"/>
+    </row>
+    <row r="235" hidden="1" outlineLevel="2">
+      <c r="A235" s="4" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="6" t="n"/>
+      <c r="D235" s="6" t="n"/>
+      <c r="E235" s="6" t="n"/>
+      <c r="F235" s="5" t="n"/>
+      <c r="G235" s="5" t="n"/>
+      <c r="H235" s="6" t="n"/>
+    </row>
+    <row r="236" hidden="1" outlineLevel="2">
+      <c r="A236" s="4" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="6" t="n"/>
+      <c r="D236" s="6" t="n"/>
+      <c r="E236" s="6" t="n"/>
+      <c r="F236" s="5" t="n"/>
+      <c r="G236" s="5" t="n"/>
+      <c r="H236" s="6" t="n"/>
+    </row>
+    <row r="237" hidden="1" outlineLevel="2">
+      <c r="A237" s="4" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="6" t="n"/>
+      <c r="D237" s="6" t="n"/>
+      <c r="E237" s="6" t="n"/>
+      <c r="F237" s="5" t="n"/>
+      <c r="G237" s="5" t="n"/>
+      <c r="H237" s="6" t="n"/>
+    </row>
+    <row r="238" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A238" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="6" t="n"/>
+      <c r="D238" s="6" t="n"/>
+      <c r="E238" s="6" t="n"/>
+      <c r="F238" s="5" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="6" t="n"/>
+    </row>
+    <row r="239" hidden="1" outlineLevel="2">
+      <c r="A239" s="4" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="6" t="n"/>
+      <c r="D239" s="6" t="n"/>
+      <c r="E239" s="6" t="n"/>
+      <c r="F239" s="5" t="n"/>
+      <c r="G239" s="5" t="n"/>
+      <c r="H239" s="6" t="n"/>
+    </row>
+    <row r="240" hidden="1" outlineLevel="2">
+      <c r="A240" s="4" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="6" t="n"/>
+      <c r="D240" s="6" t="n"/>
+      <c r="E240" s="6" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="6" t="n"/>
+    </row>
+    <row r="241" hidden="1" outlineLevel="2">
+      <c r="A241" s="4" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="6" t="n"/>
+      <c r="E241" s="6" t="n"/>
+      <c r="F241" s="5" t="n"/>
+      <c r="G241" s="5" t="n"/>
+      <c r="H241" s="6" t="n"/>
+    </row>
+    <row r="242" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A242" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B242" s="5" t="n"/>
+      <c r="C242" s="6" t="n"/>
+      <c r="D242" s="6" t="n"/>
+      <c r="E242" s="6" t="n"/>
+      <c r="F242" s="5" t="n"/>
+      <c r="G242" s="5" t="n"/>
+      <c r="H242" s="6" t="n"/>
+    </row>
+    <row r="243" hidden="1" outlineLevel="2">
+      <c r="A243" s="4" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="6" t="n"/>
+      <c r="D243" s="6" t="n"/>
+      <c r="E243" s="6" t="n"/>
+      <c r="F243" s="5" t="n"/>
+      <c r="G243" s="5" t="n"/>
+      <c r="H243" s="6" t="n"/>
+    </row>
+    <row r="244" hidden="1" outlineLevel="2">
+      <c r="A244" s="4" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="6" t="n"/>
+      <c r="E244" s="6" t="n"/>
+      <c r="F244" s="5" t="n"/>
+      <c r="G244" s="5" t="n"/>
+      <c r="H244" s="6" t="n"/>
+    </row>
+    <row r="245" hidden="1" outlineLevel="2">
+      <c r="A245" s="4" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="6" t="n"/>
+      <c r="D245" s="6" t="n"/>
+      <c r="E245" s="6" t="n"/>
+      <c r="F245" s="5" t="n"/>
+      <c r="G245" s="5" t="n"/>
+      <c r="H245" s="6" t="n"/>
+    </row>
+    <row r="246" collapsed="1">
+      <c r="A246" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B246" s="5" t="inlineStr">
         <is>
           <t>am i going under</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progWaterRipple(16550, 22, 50, true, false)
-! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = ESaite_Dis</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>progWaterRipple(16552, 13, 50, true, false), Farben SCHEME_BLUE, Farbwanderung to SCHEME_ICE, per 8
+Ausgabe: Übergang fade 2069 ms
+'am i going under': Wasserringe in Blau, weich über einen Takt eingeblendet, die Farbe wandert alle 2 Takte nach Eisblau und zurück.</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="n"/>
+      <c r="E246" s="6" t="inlineStr">
         <is>
           <t>Wasserringe bleiben (passt zum Text), in BLUE und weich eingeblendet (fade, 4 Beats); Farbwanderung nach ICE.</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5">
+      <c r="F246" s="5" t="n"/>
+      <c r="G246" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H246" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16550, 22, 50, true, false)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_Cis; markerLED6 = ESaite_Dis</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+    <row r="247" hidden="1" outlineLevel="2">
+      <c r="A247" s="4" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="6" t="n"/>
+      <c r="D247" s="6" t="n"/>
+      <c r="E247" s="6" t="n"/>
+      <c r="F247" s="5" t="n"/>
+      <c r="G247" s="5" t="n"/>
+      <c r="H247" s="6" t="n"/>
+    </row>
+    <row r="248" hidden="1" outlineLevel="2">
+      <c r="A248" s="4" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="6" t="n"/>
+      <c r="D248" s="6" t="n"/>
+      <c r="E248" s="6" t="n"/>
+      <c r="F248" s="5" t="n"/>
+      <c r="G248" s="5" t="n"/>
+      <c r="H248" s="6" t="n"/>
+    </row>
+    <row r="249" hidden="1" outlineLevel="2">
+      <c r="A249" s="4" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="6" t="n"/>
+      <c r="D249" s="6" t="n"/>
+      <c r="E249" s="6" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="6" t="n"/>
+    </row>
+    <row r="250" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A250" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="6" t="n"/>
+      <c r="D250" s="6" t="n"/>
+      <c r="E250" s="6" t="n"/>
+      <c r="F250" s="5" t="n"/>
+      <c r="G250" s="5" t="n"/>
+      <c r="H250" s="6" t="n"/>
+    </row>
+    <row r="251" hidden="1" outlineLevel="2">
+      <c r="A251" s="4" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="6" t="n"/>
+      <c r="D251" s="6" t="n"/>
+      <c r="E251" s="6" t="n"/>
+      <c r="F251" s="5" t="n"/>
+      <c r="G251" s="5" t="n"/>
+      <c r="H251" s="6" t="n"/>
+    </row>
+    <row r="252" hidden="1" outlineLevel="2">
+      <c r="A252" s="4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="6" t="n"/>
+      <c r="D252" s="6" t="n"/>
+      <c r="E252" s="6" t="n"/>
+      <c r="F252" s="5" t="n"/>
+      <c r="G252" s="5" t="n"/>
+      <c r="H252" s="6" t="n"/>
+    </row>
+    <row r="253" hidden="1" outlineLevel="2">
+      <c r="A253" s="4" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="6" t="n"/>
+      <c r="D253" s="6" t="n"/>
+      <c r="E253" s="6" t="n"/>
+      <c r="F253" s="5" t="n"/>
+      <c r="G253" s="5" t="n"/>
+      <c r="H253" s="6" t="n"/>
+    </row>
+    <row r="254" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A254" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B254" s="5" t="n"/>
+      <c r="C254" s="6" t="n"/>
+      <c r="D254" s="6" t="n"/>
+      <c r="E254" s="6" t="n"/>
+      <c r="F254" s="5" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="6" t="n"/>
+    </row>
+    <row r="255" hidden="1" outlineLevel="2">
+      <c r="A255" s="4" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="6" t="n"/>
+      <c r="D255" s="6" t="n"/>
+      <c r="E255" s="6" t="n"/>
+      <c r="F255" s="5" t="n"/>
+      <c r="G255" s="5" t="n"/>
+      <c r="H255" s="6" t="n"/>
+    </row>
+    <row r="256" hidden="1" outlineLevel="2">
+      <c r="A256" s="4" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="B256" s="5" t="n"/>
+      <c r="C256" s="6" t="n"/>
+      <c r="D256" s="6" t="n"/>
+      <c r="E256" s="6" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="6" t="n"/>
+    </row>
+    <row r="257" hidden="1" outlineLevel="2">
+      <c r="A257" s="4" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="6" t="n"/>
+      <c r="D257" s="6" t="n"/>
+      <c r="E257" s="6" t="n"/>
+      <c r="F257" s="5" t="n"/>
+      <c r="G257" s="5" t="n"/>
+      <c r="H257" s="6" t="n"/>
+    </row>
+    <row r="258" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A258" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="6" t="n"/>
+      <c r="E258" s="6" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="6" t="n"/>
+    </row>
+    <row r="259" hidden="1" outlineLevel="2">
+      <c r="A259" s="4" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="B259" s="5" t="n"/>
+      <c r="C259" s="6" t="n"/>
+      <c r="D259" s="6" t="n"/>
+      <c r="E259" s="6" t="n"/>
+      <c r="F259" s="5" t="n"/>
+      <c r="G259" s="5" t="n"/>
+      <c r="H259" s="6" t="n"/>
+    </row>
+    <row r="260" hidden="1" outlineLevel="2">
+      <c r="A260" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="6" t="n"/>
+      <c r="D260" s="6" t="n"/>
+      <c r="E260" s="6" t="n"/>
+      <c r="F260" s="5" t="n"/>
+      <c r="G260" s="5" t="n"/>
+      <c r="H260" s="6" t="n"/>
+    </row>
+    <row r="261" hidden="1" outlineLevel="2">
+      <c r="A261" s="4" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="6" t="n"/>
+      <c r="D261" s="6" t="n"/>
+      <c r="E261" s="6" t="n"/>
+      <c r="F261" s="5" t="n"/>
+      <c r="G261" s="5" t="n"/>
+      <c r="H261" s="6" t="n"/>
+    </row>
+    <row r="262" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A262" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B262" s="5" t="n"/>
+      <c r="C262" s="6" t="n"/>
+      <c r="D262" s="6" t="n"/>
+      <c r="E262" s="6" t="n"/>
+      <c r="F262" s="5" t="n"/>
+      <c r="G262" s="5" t="n"/>
+      <c r="H262" s="6" t="n"/>
+    </row>
+    <row r="263" hidden="1" outlineLevel="2">
+      <c r="A263" s="4" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="6" t="n"/>
+      <c r="D263" s="6" t="n"/>
+      <c r="E263" s="6" t="n"/>
+      <c r="F263" s="5" t="n"/>
+      <c r="G263" s="5" t="n"/>
+      <c r="H263" s="6" t="n"/>
+    </row>
+    <row r="264" hidden="1" outlineLevel="2">
+      <c r="A264" s="4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="B264" s="5" t="n"/>
+      <c r="C264" s="6" t="n"/>
+      <c r="D264" s="6" t="n"/>
+      <c r="E264" s="6" t="n"/>
+      <c r="F264" s="5" t="n"/>
+      <c r="G264" s="5" t="n"/>
+      <c r="H264" s="6" t="n"/>
+    </row>
+    <row r="265" hidden="1" outlineLevel="2">
+      <c r="A265" s="4" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="B265" s="5" t="n"/>
+      <c r="C265" s="6" t="n"/>
+      <c r="D265" s="6" t="n"/>
+      <c r="E265" s="6" t="n"/>
+      <c r="F265" s="5" t="n"/>
+      <c r="G265" s="5" t="n"/>
+      <c r="H265" s="6" t="n"/>
+    </row>
+    <row r="266" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A266" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B266" s="5" t="n"/>
+      <c r="C266" s="6" t="n"/>
+      <c r="D266" s="6" t="n"/>
+      <c r="E266" s="6" t="n"/>
+      <c r="F266" s="5" t="n"/>
+      <c r="G266" s="5" t="n"/>
+      <c r="H266" s="6" t="n"/>
+    </row>
+    <row r="267" hidden="1" outlineLevel="2">
+      <c r="A267" s="4" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="6" t="n"/>
+      <c r="D267" s="6" t="n"/>
+      <c r="E267" s="6" t="n"/>
+      <c r="F267" s="5" t="n"/>
+      <c r="G267" s="5" t="n"/>
+      <c r="H267" s="6" t="n"/>
+    </row>
+    <row r="268" hidden="1" outlineLevel="2">
+      <c r="A268" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="6" t="n"/>
+      <c r="D268" s="6" t="n"/>
+      <c r="E268" s="6" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="6" t="n"/>
+    </row>
+    <row r="269" hidden="1" outlineLevel="2">
+      <c r="A269" s="4" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="6" t="n"/>
+      <c r="E269" s="6" t="n"/>
+      <c r="F269" s="5" t="n"/>
+      <c r="G269" s="5" t="n"/>
+      <c r="H269" s="6" t="n"/>
+    </row>
+    <row r="270" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A270" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B270" s="5" t="n"/>
+      <c r="C270" s="6" t="n"/>
+      <c r="D270" s="6" t="n"/>
+      <c r="E270" s="6" t="n"/>
+      <c r="F270" s="5" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="6" t="n"/>
+    </row>
+    <row r="271" hidden="1" outlineLevel="2">
+      <c r="A271" s="4" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="B271" s="5" t="n"/>
+      <c r="C271" s="6" t="n"/>
+      <c r="D271" s="6" t="n"/>
+      <c r="E271" s="6" t="n"/>
+      <c r="F271" s="5" t="n"/>
+      <c r="G271" s="5" t="n"/>
+      <c r="H271" s="6" t="n"/>
+    </row>
+    <row r="272" hidden="1" outlineLevel="2">
+      <c r="A272" s="4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="B272" s="5" t="n"/>
+      <c r="C272" s="6" t="n"/>
+      <c r="D272" s="6" t="n"/>
+      <c r="E272" s="6" t="n"/>
+      <c r="F272" s="5" t="n"/>
+      <c r="G272" s="5" t="n"/>
+      <c r="H272" s="6" t="n"/>
+    </row>
+    <row r="273" hidden="1" outlineLevel="2">
+      <c r="A273" s="4" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="6" t="n"/>
+      <c r="D273" s="6" t="n"/>
+      <c r="E273" s="6" t="n"/>
+      <c r="F273" s="5" t="n"/>
+      <c r="G273" s="5" t="n"/>
+      <c r="H273" s="6" t="n"/>
+    </row>
+    <row r="274" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A274" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B274" s="5" t="n"/>
+      <c r="C274" s="6" t="n"/>
+      <c r="D274" s="6" t="n"/>
+      <c r="E274" s="6" t="n"/>
+      <c r="F274" s="5" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="6" t="n"/>
+    </row>
+    <row r="275" hidden="1" outlineLevel="2">
+      <c r="A275" s="4" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="6" t="n"/>
+      <c r="D275" s="6" t="n"/>
+      <c r="E275" s="6" t="n"/>
+      <c r="F275" s="5" t="n"/>
+      <c r="G275" s="5" t="n"/>
+      <c r="H275" s="6" t="n"/>
+    </row>
+    <row r="276" hidden="1" outlineLevel="2">
+      <c r="A276" s="4" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="B276" s="5" t="n"/>
+      <c r="C276" s="6" t="n"/>
+      <c r="D276" s="6" t="n"/>
+      <c r="E276" s="6" t="n"/>
+      <c r="F276" s="5" t="n"/>
+      <c r="G276" s="5" t="n"/>
+      <c r="H276" s="6" t="n"/>
+    </row>
+    <row r="277" hidden="1" outlineLevel="2">
+      <c r="A277" s="4" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="B277" s="5" t="n"/>
+      <c r="C277" s="6" t="n"/>
+      <c r="D277" s="6" t="n"/>
+      <c r="E277" s="6" t="n"/>
+      <c r="F277" s="5" t="n"/>
+      <c r="G277" s="5" t="n"/>
+      <c r="H277" s="6" t="n"/>
+    </row>
+    <row r="278" collapsed="1">
+      <c r="A278" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B278" s="5" t="inlineStr">
         <is>
           <t>bass solo</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progMatrixHorizontal(16550, 24, 70, true)
-! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = ESaite_Dis</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SOLO_BASS, Farben SCHEME_NEON
+Ausgabe: Blinder von 'chrous 3' blendet in den letzten 4138 ms ein
+Bass-Solo: zwei Kometen in Pink und Cyan kreisen um den Bass, alle anderen atmen dunkel; in den letzten 2 Takten blendet der Blinder für chrous 3 ein.</t>
+        </is>
+      </c>
+      <c r="D278" s="6" t="n"/>
+      <c r="E278" s="6" t="inlineStr">
         <is>
           <t>Szene Solo Bass, NEON: zwei Kometen laufen um den Bass, alle anderen atmen dunkel. In den letzten 2 Takten baut sich ein Blinder auf (blendet 2 Takte ein, voll auf Takt 77).</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5">
+      <c r="F278" s="5" t="n"/>
+      <c r="G278" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H278" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(16550, 24, 70, true)
 ! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = ESaite_Dis</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="279" hidden="1" outlineLevel="2">
+      <c r="A279" s="4" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="B279" s="5" t="n"/>
+      <c r="C279" s="6" t="n"/>
+      <c r="D279" s="6" t="n"/>
+      <c r="E279" s="6" t="n"/>
+      <c r="F279" s="5" t="n"/>
+      <c r="G279" s="5" t="n"/>
+      <c r="H279" s="6" t="n"/>
+    </row>
+    <row r="280" hidden="1" outlineLevel="2">
+      <c r="A280" s="4" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="B280" s="5" t="n"/>
+      <c r="C280" s="6" t="n"/>
+      <c r="D280" s="6" t="n"/>
+      <c r="E280" s="6" t="n"/>
+      <c r="F280" s="5" t="n"/>
+      <c r="G280" s="5" t="n"/>
+      <c r="H280" s="6" t="n"/>
+    </row>
+    <row r="281" hidden="1" outlineLevel="2">
+      <c r="A281" s="4" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="B281" s="5" t="n"/>
+      <c r="C281" s="6" t="n"/>
+      <c r="D281" s="6" t="n"/>
+      <c r="E281" s="6" t="n"/>
+      <c r="F281" s="5" t="n"/>
+      <c r="G281" s="5" t="n"/>
+      <c r="H281" s="6" t="n"/>
+    </row>
+    <row r="282" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A282" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B282" s="5" t="n"/>
+      <c r="C282" s="6" t="n"/>
+      <c r="D282" s="6" t="n"/>
+      <c r="E282" s="6" t="n"/>
+      <c r="F282" s="5" t="n"/>
+      <c r="G282" s="5" t="n"/>
+      <c r="H282" s="6" t="n"/>
+    </row>
+    <row r="283" hidden="1" outlineLevel="2">
+      <c r="A283" s="4" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="B283" s="5" t="n"/>
+      <c r="C283" s="6" t="n"/>
+      <c r="D283" s="6" t="n"/>
+      <c r="E283" s="6" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="5" t="n"/>
+      <c r="H283" s="6" t="n"/>
+    </row>
+    <row r="284" hidden="1" outlineLevel="2">
+      <c r="A284" s="4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="B284" s="5" t="n"/>
+      <c r="C284" s="6" t="n"/>
+      <c r="D284" s="6" t="n"/>
+      <c r="E284" s="6" t="n"/>
+      <c r="F284" s="5" t="n"/>
+      <c r="G284" s="5" t="n"/>
+      <c r="H284" s="6" t="n"/>
+    </row>
+    <row r="285" hidden="1" outlineLevel="2">
+      <c r="A285" s="4" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="B285" s="5" t="n"/>
+      <c r="C285" s="6" t="n"/>
+      <c r="D285" s="6" t="n"/>
+      <c r="E285" s="6" t="n"/>
+      <c r="F285" s="5" t="n"/>
+      <c r="G285" s="5" t="n"/>
+      <c r="H285" s="6" t="n"/>
+    </row>
+    <row r="286" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A286" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B286" s="5" t="n"/>
+      <c r="C286" s="6" t="n"/>
+      <c r="D286" s="6" t="n"/>
+      <c r="E286" s="6" t="n"/>
+      <c r="F286" s="5" t="n"/>
+      <c r="G286" s="5" t="n"/>
+      <c r="H286" s="6" t="n"/>
+    </row>
+    <row r="287" hidden="1" outlineLevel="2">
+      <c r="A287" s="4" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="B287" s="5" t="n"/>
+      <c r="C287" s="6" t="n"/>
+      <c r="D287" s="6" t="n"/>
+      <c r="E287" s="6" t="n"/>
+      <c r="F287" s="5" t="n"/>
+      <c r="G287" s="5" t="n"/>
+      <c r="H287" s="6" t="n"/>
+    </row>
+    <row r="288" hidden="1" outlineLevel="2">
+      <c r="A288" s="4" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="B288" s="5" t="n"/>
+      <c r="C288" s="6" t="n"/>
+      <c r="D288" s="6" t="n"/>
+      <c r="E288" s="6" t="n"/>
+      <c r="F288" s="5" t="n"/>
+      <c r="G288" s="5" t="n"/>
+      <c r="H288" s="6" t="n"/>
+    </row>
+    <row r="289" hidden="1" outlineLevel="2">
+      <c r="A289" s="4" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="B289" s="5" t="n"/>
+      <c r="C289" s="6" t="n"/>
+      <c r="D289" s="6" t="n"/>
+      <c r="E289" s="6" t="n"/>
+      <c r="F289" s="5" t="n"/>
+      <c r="G289" s="5" t="n"/>
+      <c r="H289" s="6" t="n"/>
+    </row>
+    <row r="290" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A290" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B290" s="5" t="n"/>
+      <c r="C290" s="6" t="n"/>
+      <c r="D290" s="6" t="n"/>
+      <c r="E290" s="6" t="n"/>
+      <c r="F290" s="5" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="6" t="n"/>
+    </row>
+    <row r="291" hidden="1" outlineLevel="2">
+      <c r="A291" s="4" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="B291" s="5" t="n"/>
+      <c r="C291" s="6" t="n"/>
+      <c r="D291" s="6" t="n"/>
+      <c r="E291" s="6" t="n"/>
+      <c r="F291" s="5" t="n"/>
+      <c r="G291" s="5" t="n"/>
+      <c r="H291" s="6" t="n"/>
+    </row>
+    <row r="292" hidden="1" outlineLevel="2">
+      <c r="A292" s="4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="B292" s="5" t="n"/>
+      <c r="C292" s="6" t="n"/>
+      <c r="D292" s="6" t="n"/>
+      <c r="E292" s="6" t="n"/>
+      <c r="F292" s="5" t="n"/>
+      <c r="G292" s="5" t="n"/>
+      <c r="H292" s="6" t="n"/>
+    </row>
+    <row r="293" hidden="1" outlineLevel="2">
+      <c r="A293" s="4" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="B293" s="5" t="n"/>
+      <c r="C293" s="6" t="n"/>
+      <c r="D293" s="6" t="n"/>
+      <c r="E293" s="6" t="n"/>
+      <c r="F293" s="5" t="n"/>
+      <c r="G293" s="5" t="n"/>
+      <c r="H293" s="6" t="n"/>
+    </row>
+    <row r="294" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A294" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B294" s="5" t="n"/>
+      <c r="C294" s="6" t="n"/>
+      <c r="D294" s="6" t="n"/>
+      <c r="E294" s="6" t="n"/>
+      <c r="F294" s="5" t="n"/>
+      <c r="G294" s="5" t="n"/>
+      <c r="H294" s="6" t="n"/>
+    </row>
+    <row r="295" hidden="1" outlineLevel="2">
+      <c r="A295" s="4" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="B295" s="5" t="n"/>
+      <c r="C295" s="6" t="n"/>
+      <c r="D295" s="6" t="n"/>
+      <c r="E295" s="6" t="n"/>
+      <c r="F295" s="5" t="n"/>
+      <c r="G295" s="5" t="n"/>
+      <c r="H295" s="6" t="n"/>
+    </row>
+    <row r="296" hidden="1" outlineLevel="2">
+      <c r="A296" s="4" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="B296" s="5" t="n"/>
+      <c r="C296" s="6" t="n"/>
+      <c r="D296" s="6" t="n"/>
+      <c r="E296" s="6" t="n"/>
+      <c r="F296" s="5" t="n"/>
+      <c r="G296" s="5" t="n"/>
+      <c r="H296" s="6" t="n"/>
+    </row>
+    <row r="297" hidden="1" outlineLevel="2">
+      <c r="A297" s="4" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="B297" s="5" t="n"/>
+      <c r="C297" s="6" t="n"/>
+      <c r="D297" s="6" t="n"/>
+      <c r="E297" s="6" t="n"/>
+      <c r="F297" s="5" t="n"/>
+      <c r="G297" s="5" t="n"/>
+      <c r="H297" s="6" t="n"/>
+    </row>
+    <row r="298" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A298" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B298" s="5" t="n"/>
+      <c r="C298" s="6" t="n"/>
+      <c r="D298" s="6" t="n"/>
+      <c r="E298" s="6" t="n"/>
+      <c r="F298" s="5" t="n"/>
+      <c r="G298" s="5" t="n"/>
+      <c r="H298" s="6" t="n"/>
+    </row>
+    <row r="299" hidden="1" outlineLevel="2">
+      <c r="A299" s="4" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="B299" s="5" t="n"/>
+      <c r="C299" s="6" t="n"/>
+      <c r="D299" s="6" t="n"/>
+      <c r="E299" s="6" t="n"/>
+      <c r="F299" s="5" t="n"/>
+      <c r="G299" s="5" t="n"/>
+      <c r="H299" s="6" t="n"/>
+    </row>
+    <row r="300" hidden="1" outlineLevel="2">
+      <c r="A300" s="4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="B300" s="5" t="n"/>
+      <c r="C300" s="6" t="n"/>
+      <c r="D300" s="6" t="n"/>
+      <c r="E300" s="6" t="n"/>
+      <c r="F300" s="5" t="n"/>
+      <c r="G300" s="5" t="n"/>
+      <c r="H300" s="6" t="n"/>
+    </row>
+    <row r="301" hidden="1" outlineLevel="2">
+      <c r="A301" s="4" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="B301" s="5" t="n"/>
+      <c r="C301" s="6" t="n"/>
+      <c r="D301" s="6" t="n"/>
+      <c r="E301" s="6" t="n"/>
+      <c r="F301" s="5" t="n"/>
+      <c r="G301" s="5" t="n"/>
+      <c r="H301" s="6" t="n"/>
+    </row>
+    <row r="302" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A302" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B302" s="5" t="n"/>
+      <c r="C302" s="6" t="n"/>
+      <c r="D302" s="6" t="n"/>
+      <c r="E302" s="6" t="n"/>
+      <c r="F302" s="5" t="n"/>
+      <c r="G302" s="5" t="n"/>
+      <c r="H302" s="6" t="n"/>
+    </row>
+    <row r="303" hidden="1" outlineLevel="2">
+      <c r="A303" s="4" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="B303" s="5" t="n"/>
+      <c r="C303" s="6" t="n"/>
+      <c r="D303" s="6" t="n"/>
+      <c r="E303" s="6" t="n"/>
+      <c r="F303" s="5" t="n"/>
+      <c r="G303" s="5" t="n"/>
+      <c r="H303" s="6" t="n"/>
+    </row>
+    <row r="304" hidden="1" outlineLevel="2">
+      <c r="A304" s="4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="B304" s="5" t="n"/>
+      <c r="C304" s="6" t="n"/>
+      <c r="D304" s="6" t="n"/>
+      <c r="E304" s="6" t="n"/>
+      <c r="F304" s="5" t="n"/>
+      <c r="G304" s="5" t="n"/>
+      <c r="H304" s="6" t="n"/>
+    </row>
+    <row r="305" hidden="1" outlineLevel="2">
+      <c r="A305" s="4" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="B305" s="5" t="n"/>
+      <c r="C305" s="6" t="n"/>
+      <c r="D305" s="6" t="n"/>
+      <c r="E305" s="6" t="n"/>
+      <c r="F305" s="5" t="n"/>
+      <c r="G305" s="5" t="n"/>
+      <c r="H305" s="6" t="n"/>
+    </row>
+    <row r="306" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A306" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B306" s="5" t="n"/>
+      <c r="C306" s="6" t="n"/>
+      <c r="D306" s="6" t="n"/>
+      <c r="E306" s="6" t="n"/>
+      <c r="F306" s="5" t="n"/>
+      <c r="G306" s="5" t="n"/>
+      <c r="H306" s="6" t="n"/>
+    </row>
+    <row r="307" hidden="1" outlineLevel="2">
+      <c r="A307" s="4" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="B307" s="5" t="n"/>
+      <c r="C307" s="6" t="n"/>
+      <c r="D307" s="6" t="n"/>
+      <c r="E307" s="6" t="n"/>
+      <c r="F307" s="5" t="n"/>
+      <c r="G307" s="5" t="n"/>
+      <c r="H307" s="6" t="n"/>
+    </row>
+    <row r="308" hidden="1" outlineLevel="2">
+      <c r="A308" s="4" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="B308" s="5" t="n"/>
+      <c r="C308" s="6" t="n"/>
+      <c r="D308" s="6" t="n"/>
+      <c r="E308" s="6" t="n"/>
+      <c r="F308" s="5" t="n"/>
+      <c r="G308" s="5" t="n"/>
+      <c r="H308" s="6" t="n"/>
+    </row>
+    <row r="309" hidden="1" outlineLevel="2">
+      <c r="A309" s="4" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="B309" s="5" t="n"/>
+      <c r="C309" s="6" t="n"/>
+      <c r="D309" s="6" t="n"/>
+      <c r="E309" s="6" t="n"/>
+      <c r="F309" s="5" t="n"/>
+      <c r="G309" s="5" t="n"/>
+      <c r="H309" s="6" t="n"/>
+    </row>
+    <row r="310" collapsed="1">
+      <c r="A310" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B310" s="5" t="inlineStr">
         <is>
           <t>chrous 3</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progSternNeu(16550, 515, 26, 5, 26, 5, true, 3)
-! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = 0</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_SUNSET
+Ausgabe: Blinder voll bei Takt 77 = 0 ms, 5172 ms lang, Blinder blendet in den 4138 ms davor ein, 0 ms voll, 1034 ms aus
+Eine Stufe wärmer: Stern in Orange, Pink, Lila und Gelb. Der Blinder blendet über die letzten 2 Takte des Bass-Solos ein, steht voll auf dem Einsatz (Takt 77) und klingt in 2 Beats ab.</t>
+        </is>
+      </c>
+      <c r="D310" s="6" t="n"/>
+      <c r="E310" s="6" t="inlineStr">
         <is>
           <t>Szene Star, SUNSET - eine Stufe wärmer, der Blinder vom Bass-Solo steht auf dem Einsatz.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
+      <c r="F310" s="5" t="n"/>
+      <c r="G310" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H310" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16550, 515, 26, 5, 26, 5, true, 3)
 ! der alte Code setzt hier Marker: markerLED5 = 0; markerLED6 = 0</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+    <row r="311" hidden="1" outlineLevel="2">
+      <c r="A311" s="4" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="B311" s="5" t="n"/>
+      <c r="C311" s="6" t="n"/>
+      <c r="D311" s="6" t="n"/>
+      <c r="E311" s="6" t="n"/>
+      <c r="F311" s="5" t="n"/>
+      <c r="G311" s="5" t="n"/>
+      <c r="H311" s="6" t="n"/>
+    </row>
+    <row r="312" hidden="1" outlineLevel="2">
+      <c r="A312" s="4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="B312" s="5" t="n"/>
+      <c r="C312" s="6" t="n"/>
+      <c r="D312" s="6" t="n"/>
+      <c r="E312" s="6" t="n"/>
+      <c r="F312" s="5" t="n"/>
+      <c r="G312" s="5" t="n"/>
+      <c r="H312" s="6" t="n"/>
+    </row>
+    <row r="313" hidden="1" outlineLevel="2">
+      <c r="A313" s="4" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="B313" s="5" t="n"/>
+      <c r="C313" s="6" t="n"/>
+      <c r="D313" s="6" t="n"/>
+      <c r="E313" s="6" t="n"/>
+      <c r="F313" s="5" t="n"/>
+      <c r="G313" s="5" t="n"/>
+      <c r="H313" s="6" t="n"/>
+    </row>
+    <row r="314" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A314" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B314" s="5" t="n"/>
+      <c r="C314" s="6" t="n"/>
+      <c r="D314" s="6" t="n"/>
+      <c r="E314" s="6" t="n"/>
+      <c r="F314" s="5" t="n"/>
+      <c r="G314" s="5" t="n"/>
+      <c r="H314" s="6" t="n"/>
+    </row>
+    <row r="315" hidden="1" outlineLevel="2">
+      <c r="A315" s="4" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="B315" s="5" t="n"/>
+      <c r="C315" s="6" t="n"/>
+      <c r="D315" s="6" t="n"/>
+      <c r="E315" s="6" t="n"/>
+      <c r="F315" s="5" t="n"/>
+      <c r="G315" s="5" t="n"/>
+      <c r="H315" s="6" t="n"/>
+    </row>
+    <row r="316" hidden="1" outlineLevel="2">
+      <c r="A316" s="4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="B316" s="5" t="n"/>
+      <c r="C316" s="6" t="n"/>
+      <c r="D316" s="6" t="n"/>
+      <c r="E316" s="6" t="n"/>
+      <c r="F316" s="5" t="n"/>
+      <c r="G316" s="5" t="n"/>
+      <c r="H316" s="6" t="n"/>
+    </row>
+    <row r="317" hidden="1" outlineLevel="2">
+      <c r="A317" s="4" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="B317" s="5" t="n"/>
+      <c r="C317" s="6" t="n"/>
+      <c r="D317" s="6" t="n"/>
+      <c r="E317" s="6" t="n"/>
+      <c r="F317" s="5" t="n"/>
+      <c r="G317" s="5" t="n"/>
+      <c r="H317" s="6" t="n"/>
+    </row>
+    <row r="318" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A318" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B318" s="5" t="n"/>
+      <c r="C318" s="6" t="n"/>
+      <c r="D318" s="6" t="n"/>
+      <c r="E318" s="6" t="n"/>
+      <c r="F318" s="5" t="n"/>
+      <c r="G318" s="5" t="n"/>
+      <c r="H318" s="6" t="n"/>
+    </row>
+    <row r="319" hidden="1" outlineLevel="2">
+      <c r="A319" s="4" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="B319" s="5" t="n"/>
+      <c r="C319" s="6" t="n"/>
+      <c r="D319" s="6" t="n"/>
+      <c r="E319" s="6" t="n"/>
+      <c r="F319" s="5" t="n"/>
+      <c r="G319" s="5" t="n"/>
+      <c r="H319" s="6" t="n"/>
+    </row>
+    <row r="320" hidden="1" outlineLevel="2">
+      <c r="A320" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="B320" s="5" t="n"/>
+      <c r="C320" s="6" t="n"/>
+      <c r="D320" s="6" t="n"/>
+      <c r="E320" s="6" t="n"/>
+      <c r="F320" s="5" t="n"/>
+      <c r="G320" s="5" t="n"/>
+      <c r="H320" s="6" t="n"/>
+    </row>
+    <row r="321" hidden="1" outlineLevel="2">
+      <c r="A321" s="4" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="B321" s="5" t="n"/>
+      <c r="C321" s="6" t="n"/>
+      <c r="D321" s="6" t="n"/>
+      <c r="E321" s="6" t="n"/>
+      <c r="F321" s="5" t="n"/>
+      <c r="G321" s="5" t="n"/>
+      <c r="H321" s="6" t="n"/>
+    </row>
+    <row r="322" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A322" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B322" s="5" t="n"/>
+      <c r="C322" s="6" t="n"/>
+      <c r="D322" s="6" t="n"/>
+      <c r="E322" s="6" t="n"/>
+      <c r="F322" s="5" t="n"/>
+      <c r="G322" s="5" t="n"/>
+      <c r="H322" s="6" t="n"/>
+    </row>
+    <row r="323" hidden="1" outlineLevel="2">
+      <c r="A323" s="4" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="B323" s="5" t="n"/>
+      <c r="C323" s="6" t="n"/>
+      <c r="D323" s="6" t="n"/>
+      <c r="E323" s="6" t="n"/>
+      <c r="F323" s="5" t="n"/>
+      <c r="G323" s="5" t="n"/>
+      <c r="H323" s="6" t="n"/>
+    </row>
+    <row r="324" hidden="1" outlineLevel="2">
+      <c r="A324" s="4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="B324" s="5" t="n"/>
+      <c r="C324" s="6" t="n"/>
+      <c r="D324" s="6" t="n"/>
+      <c r="E324" s="6" t="n"/>
+      <c r="F324" s="5" t="n"/>
+      <c r="G324" s="5" t="n"/>
+      <c r="H324" s="6" t="n"/>
+    </row>
+    <row r="325" hidden="1" outlineLevel="2">
+      <c r="A325" s="4" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="B325" s="5" t="n"/>
+      <c r="C325" s="6" t="n"/>
+      <c r="D325" s="6" t="n"/>
+      <c r="E325" s="6" t="n"/>
+      <c r="F325" s="5" t="n"/>
+      <c r="G325" s="5" t="n"/>
+      <c r="H325" s="6" t="n"/>
+    </row>
+    <row r="326" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A326" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B326" s="5" t="n"/>
+      <c r="C326" s="6" t="n"/>
+      <c r="D326" s="6" t="n"/>
+      <c r="E326" s="6" t="n"/>
+      <c r="F326" s="5" t="n"/>
+      <c r="G326" s="5" t="n"/>
+      <c r="H326" s="6" t="n"/>
+    </row>
+    <row r="327" hidden="1" outlineLevel="2">
+      <c r="A327" s="4" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="B327" s="5" t="n"/>
+      <c r="C327" s="6" t="n"/>
+      <c r="D327" s="6" t="n"/>
+      <c r="E327" s="6" t="n"/>
+      <c r="F327" s="5" t="n"/>
+      <c r="G327" s="5" t="n"/>
+      <c r="H327" s="6" t="n"/>
+    </row>
+    <row r="328" hidden="1" outlineLevel="2">
+      <c r="A328" s="4" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="B328" s="5" t="n"/>
+      <c r="C328" s="6" t="n"/>
+      <c r="D328" s="6" t="n"/>
+      <c r="E328" s="6" t="n"/>
+      <c r="F328" s="5" t="n"/>
+      <c r="G328" s="5" t="n"/>
+      <c r="H328" s="6" t="n"/>
+    </row>
+    <row r="329" hidden="1" outlineLevel="2">
+      <c r="A329" s="4" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="B329" s="5" t="n"/>
+      <c r="C329" s="6" t="n"/>
+      <c r="D329" s="6" t="n"/>
+      <c r="E329" s="6" t="n"/>
+      <c r="F329" s="5" t="n"/>
+      <c r="G329" s="5" t="n"/>
+      <c r="H329" s="6" t="n"/>
+    </row>
+    <row r="330" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A330" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B330" s="5" t="n"/>
+      <c r="C330" s="6" t="n"/>
+      <c r="D330" s="6" t="n"/>
+      <c r="E330" s="6" t="n"/>
+      <c r="F330" s="5" t="n"/>
+      <c r="G330" s="5" t="n"/>
+      <c r="H330" s="6" t="n"/>
+    </row>
+    <row r="331" hidden="1" outlineLevel="2">
+      <c r="A331" s="4" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="B331" s="5" t="n"/>
+      <c r="C331" s="6" t="n"/>
+      <c r="D331" s="6" t="n"/>
+      <c r="E331" s="6" t="n"/>
+      <c r="F331" s="5" t="n"/>
+      <c r="G331" s="5" t="n"/>
+      <c r="H331" s="6" t="n"/>
+    </row>
+    <row r="332" hidden="1" outlineLevel="2">
+      <c r="A332" s="4" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="B332" s="5" t="n"/>
+      <c r="C332" s="6" t="n"/>
+      <c r="D332" s="6" t="n"/>
+      <c r="E332" s="6" t="n"/>
+      <c r="F332" s="5" t="n"/>
+      <c r="G332" s="5" t="n"/>
+      <c r="H332" s="6" t="n"/>
+    </row>
+    <row r="333" hidden="1" outlineLevel="2">
+      <c r="A333" s="4" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="B333" s="5" t="n"/>
+      <c r="C333" s="6" t="n"/>
+      <c r="D333" s="6" t="n"/>
+      <c r="E333" s="6" t="n"/>
+      <c r="F333" s="5" t="n"/>
+      <c r="G333" s="5" t="n"/>
+      <c r="H333" s="6" t="n"/>
+    </row>
+    <row r="334" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A334" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B334" s="5" t="n"/>
+      <c r="C334" s="6" t="n"/>
+      <c r="D334" s="6" t="n"/>
+      <c r="E334" s="6" t="n"/>
+      <c r="F334" s="5" t="n"/>
+      <c r="G334" s="5" t="n"/>
+      <c r="H334" s="6" t="n"/>
+    </row>
+    <row r="335" hidden="1" outlineLevel="2">
+      <c r="A335" s="4" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="B335" s="5" t="n"/>
+      <c r="C335" s="6" t="n"/>
+      <c r="D335" s="6" t="n"/>
+      <c r="E335" s="6" t="n"/>
+      <c r="F335" s="5" t="n"/>
+      <c r="G335" s="5" t="n"/>
+      <c r="H335" s="6" t="n"/>
+    </row>
+    <row r="336" hidden="1" outlineLevel="2">
+      <c r="A336" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="B336" s="5" t="n"/>
+      <c r="C336" s="6" t="n"/>
+      <c r="D336" s="6" t="n"/>
+      <c r="E336" s="6" t="n"/>
+      <c r="F336" s="5" t="n"/>
+      <c r="G336" s="5" t="n"/>
+      <c r="H336" s="6" t="n"/>
+    </row>
+    <row r="337" hidden="1" outlineLevel="2">
+      <c r="A337" s="4" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="B337" s="5" t="n"/>
+      <c r="C337" s="6" t="n"/>
+      <c r="D337" s="6" t="n"/>
+      <c r="E337" s="6" t="n"/>
+      <c r="F337" s="5" t="n"/>
+      <c r="G337" s="5" t="n"/>
+      <c r="H337" s="6" t="n"/>
+    </row>
+    <row r="338" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A338" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B338" s="5" t="n"/>
+      <c r="C338" s="6" t="n"/>
+      <c r="D338" s="6" t="n"/>
+      <c r="E338" s="6" t="n"/>
+      <c r="F338" s="5" t="n"/>
+      <c r="G338" s="5" t="n"/>
+      <c r="H338" s="6" t="n"/>
+    </row>
+    <row r="339" hidden="1" outlineLevel="2">
+      <c r="A339" s="4" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="B339" s="5" t="n"/>
+      <c r="C339" s="6" t="n"/>
+      <c r="D339" s="6" t="n"/>
+      <c r="E339" s="6" t="n"/>
+      <c r="F339" s="5" t="n"/>
+      <c r="G339" s="5" t="n"/>
+      <c r="H339" s="6" t="n"/>
+    </row>
+    <row r="340" hidden="1" outlineLevel="2">
+      <c r="A340" s="4" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="B340" s="5" t="n"/>
+      <c r="C340" s="6" t="n"/>
+      <c r="D340" s="6" t="n"/>
+      <c r="E340" s="6" t="n"/>
+      <c r="F340" s="5" t="n"/>
+      <c r="G340" s="5" t="n"/>
+      <c r="H340" s="6" t="n"/>
+    </row>
+    <row r="341" hidden="1" outlineLevel="2">
+      <c r="A341" s="4" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="B341" s="5" t="n"/>
+      <c r="C341" s="6" t="n"/>
+      <c r="D341" s="6" t="n"/>
+      <c r="E341" s="6" t="n"/>
+      <c r="F341" s="5" t="n"/>
+      <c r="G341" s="5" t="n"/>
+      <c r="H341" s="6" t="n"/>
+    </row>
+    <row r="342" collapsed="1">
+      <c r="A342" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B342" s="5" t="inlineStr">
         <is>
           <t>chorus 4</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progFastBlingBling(16550, 8, 28)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="C342" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_FIRE
+Ausgabe: Blinder voll bei Takt 88,5 = 7241 ms, 414 ms lang, Blinder blendet in den 103 ms davor ein, 103 ms voll, 208 ms aus, Blinder voll bei Takt 88,75 = 7759 ms, 414 ms lang, Blinder blendet in den 103 ms davor ein, 103 ms voll, 208 ms aus, Blinder voll bei Takt 89 = 8276 ms, 414 ms lang, Blinder blendet in den 103 ms davor ein, 103 ms voll, 208 ms aus, Blinder bei Takt 92,75 = 16034 ms, 2069 ms lang, Blinder blendet 0 ms ein, 259 ms voll, 1810 ms aus
+Dichtes Glitzern in Rot, Orange und Gelb; drei kurze Blinder am Ende des 4. Takts (Takt 88,5 / 88,75 / 89) und ein starker Blinder auf der letzten Viertel (Takt 92,75), der ins Fade-out ausklingt.</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="n"/>
+      <c r="E342" s="6" t="inlineStr">
         <is>
           <t>Szene Sparkle, FIRE; drei kurze Blinder Ende des 4. Takts (Takt 88,5 / 88,75 / 89); starker Blinder auf der letzten Viertel (Takt 92,75), klingt ins Fade-out aus (carry).</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
+      <c r="F342" s="5" t="n"/>
+      <c r="G342" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H342" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16550, 8, 28)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="343" hidden="1" outlineLevel="2">
+      <c r="A343" s="4" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="B343" s="5" t="n"/>
+      <c r="C343" s="6" t="n"/>
+      <c r="D343" s="6" t="n"/>
+      <c r="E343" s="6" t="n"/>
+      <c r="F343" s="5" t="n"/>
+      <c r="G343" s="5" t="n"/>
+      <c r="H343" s="6" t="n"/>
+    </row>
+    <row r="344" hidden="1" outlineLevel="2">
+      <c r="A344" s="4" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="B344" s="5" t="n"/>
+      <c r="C344" s="6" t="n"/>
+      <c r="D344" s="6" t="n"/>
+      <c r="E344" s="6" t="n"/>
+      <c r="F344" s="5" t="n"/>
+      <c r="G344" s="5" t="n"/>
+      <c r="H344" s="6" t="n"/>
+    </row>
+    <row r="345" hidden="1" outlineLevel="2">
+      <c r="A345" s="4" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="B345" s="5" t="n"/>
+      <c r="C345" s="6" t="n"/>
+      <c r="D345" s="6" t="n"/>
+      <c r="E345" s="6" t="n"/>
+      <c r="F345" s="5" t="n"/>
+      <c r="G345" s="5" t="n"/>
+      <c r="H345" s="6" t="n"/>
+    </row>
+    <row r="346" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A346" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B346" s="5" t="n"/>
+      <c r="C346" s="6" t="n"/>
+      <c r="D346" s="6" t="n"/>
+      <c r="E346" s="6" t="n"/>
+      <c r="F346" s="5" t="n"/>
+      <c r="G346" s="5" t="n"/>
+      <c r="H346" s="6" t="n"/>
+    </row>
+    <row r="347" hidden="1" outlineLevel="2">
+      <c r="A347" s="4" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="B347" s="5" t="n"/>
+      <c r="C347" s="6" t="n"/>
+      <c r="D347" s="6" t="n"/>
+      <c r="E347" s="6" t="n"/>
+      <c r="F347" s="5" t="n"/>
+      <c r="G347" s="5" t="n"/>
+      <c r="H347" s="6" t="n"/>
+    </row>
+    <row r="348" hidden="1" outlineLevel="2">
+      <c r="A348" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="B348" s="5" t="n"/>
+      <c r="C348" s="6" t="n"/>
+      <c r="D348" s="6" t="n"/>
+      <c r="E348" s="6" t="n"/>
+      <c r="F348" s="5" t="n"/>
+      <c r="G348" s="5" t="n"/>
+      <c r="H348" s="6" t="n"/>
+    </row>
+    <row r="349" hidden="1" outlineLevel="2">
+      <c r="A349" s="4" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="B349" s="5" t="n"/>
+      <c r="C349" s="6" t="n"/>
+      <c r="D349" s="6" t="n"/>
+      <c r="E349" s="6" t="n"/>
+      <c r="F349" s="5" t="n"/>
+      <c r="G349" s="5" t="n"/>
+      <c r="H349" s="6" t="n"/>
+    </row>
+    <row r="350" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A350" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B350" s="5" t="n"/>
+      <c r="C350" s="6" t="n"/>
+      <c r="D350" s="6" t="n"/>
+      <c r="E350" s="6" t="n"/>
+      <c r="F350" s="5" t="n"/>
+      <c r="G350" s="5" t="n"/>
+      <c r="H350" s="6" t="n"/>
+    </row>
+    <row r="351" hidden="1" outlineLevel="2">
+      <c r="A351" s="4" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="B351" s="5" t="n"/>
+      <c r="C351" s="6" t="n"/>
+      <c r="D351" s="6" t="n"/>
+      <c r="E351" s="6" t="n"/>
+      <c r="F351" s="5" t="n"/>
+      <c r="G351" s="5" t="n"/>
+      <c r="H351" s="6" t="n"/>
+    </row>
+    <row r="352" hidden="1" outlineLevel="2">
+      <c r="A352" s="4" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="B352" s="5" t="n"/>
+      <c r="C352" s="6" t="n"/>
+      <c r="D352" s="6" t="n"/>
+      <c r="E352" s="6" t="n"/>
+      <c r="F352" s="5" t="n"/>
+      <c r="G352" s="5" t="n"/>
+      <c r="H352" s="6" t="n"/>
+    </row>
+    <row r="353" hidden="1" outlineLevel="2">
+      <c r="A353" s="4" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="B353" s="5" t="n"/>
+      <c r="C353" s="6" t="n"/>
+      <c r="D353" s="6" t="n"/>
+      <c r="E353" s="6" t="n"/>
+      <c r="F353" s="5" t="n"/>
+      <c r="G353" s="5" t="n"/>
+      <c r="H353" s="6" t="n"/>
+    </row>
+    <row r="354" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A354" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B354" s="5" t="n"/>
+      <c r="C354" s="6" t="n"/>
+      <c r="D354" s="6" t="n"/>
+      <c r="E354" s="6" t="n"/>
+      <c r="F354" s="5" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="6" t="n"/>
+    </row>
+    <row r="355" hidden="1" outlineLevel="2">
+      <c r="A355" s="4" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="B355" s="5" t="n"/>
+      <c r="C355" s="6" t="n"/>
+      <c r="D355" s="6" t="n"/>
+      <c r="E355" s="6" t="n"/>
+      <c r="F355" s="5" t="n"/>
+      <c r="G355" s="5" t="n"/>
+      <c r="H355" s="6" t="n"/>
+    </row>
+    <row r="356" hidden="1" outlineLevel="2">
+      <c r="A356" s="4" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="B356" s="5" t="n"/>
+      <c r="C356" s="6" t="n"/>
+      <c r="D356" s="6" t="n"/>
+      <c r="E356" s="6" t="n"/>
+      <c r="F356" s="5" t="n"/>
+      <c r="G356" s="5" t="n"/>
+      <c r="H356" s="6" t="n"/>
+    </row>
+    <row r="357" hidden="1" outlineLevel="2">
+      <c r="A357" s="4" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="B357" s="5" t="n"/>
+      <c r="C357" s="6" t="n"/>
+      <c r="D357" s="6" t="n"/>
+      <c r="E357" s="6" t="n"/>
+      <c r="F357" s="5" t="n"/>
+      <c r="G357" s="5" t="n"/>
+      <c r="H357" s="6" t="n"/>
+    </row>
+    <row r="358" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A358" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B358" s="5" t="n"/>
+      <c r="C358" s="6" t="n"/>
+      <c r="D358" s="6" t="n"/>
+      <c r="E358" s="6" t="n"/>
+      <c r="F358" s="5" t="n"/>
+      <c r="G358" s="5" t="n"/>
+      <c r="H358" s="6" t="n"/>
+    </row>
+    <row r="359" hidden="1" outlineLevel="2">
+      <c r="A359" s="4" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="B359" s="5" t="n"/>
+      <c r="C359" s="6" t="n"/>
+      <c r="D359" s="6" t="n"/>
+      <c r="E359" s="6" t="n"/>
+      <c r="F359" s="5" t="n"/>
+      <c r="G359" s="5" t="n"/>
+      <c r="H359" s="6" t="n"/>
+    </row>
+    <row r="360" hidden="1" outlineLevel="2">
+      <c r="A360" s="4" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="B360" s="5" t="n"/>
+      <c r="C360" s="6" t="n"/>
+      <c r="D360" s="6" t="n"/>
+      <c r="E360" s="6" t="n"/>
+      <c r="F360" s="5" t="n"/>
+      <c r="G360" s="5" t="n"/>
+      <c r="H360" s="6" t="n"/>
+    </row>
+    <row r="361" hidden="1" outlineLevel="2">
+      <c r="A361" s="4" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="B361" s="5" t="n"/>
+      <c r="C361" s="6" t="n"/>
+      <c r="D361" s="6" t="n"/>
+      <c r="E361" s="6" t="n"/>
+      <c r="F361" s="5" t="n"/>
+      <c r="G361" s="5" t="n"/>
+      <c r="H361" s="6" t="n"/>
+    </row>
+    <row r="362" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A362" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B362" s="5" t="n"/>
+      <c r="C362" s="6" t="n"/>
+      <c r="D362" s="6" t="n"/>
+      <c r="E362" s="6" t="n"/>
+      <c r="F362" s="5" t="n"/>
+      <c r="G362" s="5" t="n"/>
+      <c r="H362" s="6" t="n"/>
+    </row>
+    <row r="363" hidden="1" outlineLevel="2">
+      <c r="A363" s="4" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="B363" s="5" t="n"/>
+      <c r="C363" s="6" t="n"/>
+      <c r="D363" s="6" t="n"/>
+      <c r="E363" s="6" t="n"/>
+      <c r="F363" s="5" t="n"/>
+      <c r="G363" s="5" t="n"/>
+      <c r="H363" s="6" t="n"/>
+    </row>
+    <row r="364" hidden="1" outlineLevel="2">
+      <c r="A364" s="4" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="B364" s="5" t="n"/>
+      <c r="C364" s="6" t="n"/>
+      <c r="D364" s="6" t="n"/>
+      <c r="E364" s="6" t="n"/>
+      <c r="F364" s="5" t="n"/>
+      <c r="G364" s="5" t="n"/>
+      <c r="H364" s="6" t="n"/>
+    </row>
+    <row r="365" hidden="1" outlineLevel="2">
+      <c r="A365" s="4" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="B365" s="5" t="n"/>
+      <c r="C365" s="6" t="n"/>
+      <c r="D365" s="6" t="n"/>
+      <c r="E365" s="6" t="n"/>
+      <c r="F365" s="5" t="n"/>
+      <c r="G365" s="5" t="n"/>
+      <c r="H365" s="6" t="n"/>
+    </row>
+    <row r="366" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A366" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B366" s="5" t="n"/>
+      <c r="C366" s="6" t="n"/>
+      <c r="D366" s="6" t="n"/>
+      <c r="E366" s="6" t="n"/>
+      <c r="F366" s="5" t="n"/>
+      <c r="G366" s="5" t="n"/>
+      <c r="H366" s="6" t="n"/>
+    </row>
+    <row r="367" hidden="1" outlineLevel="2">
+      <c r="A367" s="4" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="B367" s="5" t="n"/>
+      <c r="C367" s="6" t="n"/>
+      <c r="D367" s="6" t="n"/>
+      <c r="E367" s="6" t="n"/>
+      <c r="F367" s="5" t="n"/>
+      <c r="G367" s="5" t="n"/>
+      <c r="H367" s="6" t="n"/>
+    </row>
+    <row r="368" hidden="1" outlineLevel="2">
+      <c r="A368" s="4" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="B368" s="5" t="n"/>
+      <c r="C368" s="6" t="n"/>
+      <c r="D368" s="6" t="n"/>
+      <c r="E368" s="6" t="n"/>
+      <c r="F368" s="5" t="n"/>
+      <c r="G368" s="5" t="n"/>
+      <c r="H368" s="6" t="n"/>
+    </row>
+    <row r="369" hidden="1" outlineLevel="2">
+      <c r="A369" s="4" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="B369" s="5" t="n"/>
+      <c r="C369" s="6" t="n"/>
+      <c r="D369" s="6" t="n"/>
+      <c r="E369" s="6" t="n"/>
+      <c r="F369" s="5" t="n"/>
+      <c r="G369" s="5" t="n"/>
+      <c r="H369" s="6" t="n"/>
+    </row>
+    <row r="370" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A370" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B370" s="5" t="n"/>
+      <c r="C370" s="6" t="n"/>
+      <c r="D370" s="6" t="n"/>
+      <c r="E370" s="6" t="n"/>
+      <c r="F370" s="5" t="n"/>
+      <c r="G370" s="5" t="n"/>
+      <c r="H370" s="6" t="n"/>
+    </row>
+    <row r="371" hidden="1" outlineLevel="2">
+      <c r="A371" s="4" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="B371" s="5" t="n"/>
+      <c r="C371" s="6" t="n"/>
+      <c r="D371" s="6" t="n"/>
+      <c r="E371" s="6" t="n"/>
+      <c r="F371" s="5" t="n"/>
+      <c r="G371" s="5" t="n"/>
+      <c r="H371" s="6" t="n"/>
+    </row>
+    <row r="372" hidden="1" outlineLevel="2">
+      <c r="A372" s="4" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="B372" s="5" t="n"/>
+      <c r="C372" s="6" t="n"/>
+      <c r="D372" s="6" t="n"/>
+      <c r="E372" s="6" t="n"/>
+      <c r="F372" s="5" t="n"/>
+      <c r="G372" s="5" t="n"/>
+      <c r="H372" s="6" t="n"/>
+    </row>
+    <row r="373" hidden="1" outlineLevel="2">
+      <c r="A373" s="4" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="B373" s="5" t="n"/>
+      <c r="C373" s="6" t="n"/>
+      <c r="D373" s="6" t="n"/>
+      <c r="E373" s="6" t="n"/>
+      <c r="F373" s="5" t="n"/>
+      <c r="G373" s="5" t="n"/>
+      <c r="H373" s="6" t="n"/>
+    </row>
+    <row r="374" collapsed="1">
+      <c r="A374" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B374" s="5" t="inlineStr">
         <is>
           <t>fade out</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>alter Code (handgeschrieben, läuft so in der Firmware):
-progBlingBlingColoring(6200, 30, 5000)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="C374" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_FADEOUT, Farben SCHEME_ROYAL
+Ausgabe: Blinder von 'chorus 4' klingt noch 1551 ms aus
+Blau und Lila, blendet über die 3 Takte weich nach Schwarz.</t>
+        </is>
+      </c>
+      <c r="D374" s="6" t="n"/>
+      <c r="E374" s="6" t="inlineStr">
         <is>
           <t>Szene Fadeout, ROYAL: blendet über die 3 Takte weich nach Schwarz.</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
+      <c r="F374" s="5" t="n"/>
+      <c r="G374" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H374" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(6200, 30, 5000)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
+    <row r="375" hidden="1" outlineLevel="2">
+      <c r="A375" s="4" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="B375" s="5" t="n"/>
+      <c r="C375" s="6" t="n"/>
+      <c r="D375" s="6" t="n"/>
+      <c r="E375" s="6" t="n"/>
+      <c r="F375" s="5" t="n"/>
+      <c r="G375" s="5" t="n"/>
+      <c r="H375" s="6" t="n"/>
+    </row>
+    <row r="376" hidden="1" outlineLevel="2">
+      <c r="A376" s="4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="B376" s="5" t="n"/>
+      <c r="C376" s="6" t="n"/>
+      <c r="D376" s="6" t="n"/>
+      <c r="E376" s="6" t="n"/>
+      <c r="F376" s="5" t="n"/>
+      <c r="G376" s="5" t="n"/>
+      <c r="H376" s="6" t="n"/>
+    </row>
+    <row r="377" hidden="1" outlineLevel="2">
+      <c r="A377" s="4" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="B377" s="5" t="n"/>
+      <c r="C377" s="6" t="n"/>
+      <c r="D377" s="6" t="n"/>
+      <c r="E377" s="6" t="n"/>
+      <c r="F377" s="5" t="n"/>
+      <c r="G377" s="5" t="n"/>
+      <c r="H377" s="6" t="n"/>
+    </row>
+    <row r="378" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A378" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B378" s="5" t="n"/>
+      <c r="C378" s="6" t="n"/>
+      <c r="D378" s="6" t="n"/>
+      <c r="E378" s="6" t="n"/>
+      <c r="F378" s="5" t="n"/>
+      <c r="G378" s="5" t="n"/>
+      <c r="H378" s="6" t="n"/>
+    </row>
+    <row r="379" hidden="1" outlineLevel="2">
+      <c r="A379" s="4" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="B379" s="5" t="n"/>
+      <c r="C379" s="6" t="n"/>
+      <c r="D379" s="6" t="n"/>
+      <c r="E379" s="6" t="n"/>
+      <c r="F379" s="5" t="n"/>
+      <c r="G379" s="5" t="n"/>
+      <c r="H379" s="6" t="n"/>
+    </row>
+    <row r="380" hidden="1" outlineLevel="2">
+      <c r="A380" s="4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="B380" s="5" t="n"/>
+      <c r="C380" s="6" t="n"/>
+      <c r="D380" s="6" t="n"/>
+      <c r="E380" s="6" t="n"/>
+      <c r="F380" s="5" t="n"/>
+      <c r="G380" s="5" t="n"/>
+      <c r="H380" s="6" t="n"/>
+    </row>
+    <row r="381" hidden="1" outlineLevel="2">
+      <c r="A381" s="4" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="B381" s="5" t="n"/>
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+      <c r="E381" s="6" t="n"/>
+      <c r="F381" s="5" t="n"/>
+      <c r="G381" s="5" t="n"/>
+      <c r="H381" s="6" t="n"/>
+    </row>
+    <row r="382" hidden="1" outlineLevel="1" collapsed="1">
+      <c r="A382" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B382" s="5" t="n"/>
+      <c r="C382" s="6" t="n"/>
+      <c r="D382" s="6" t="n"/>
+      <c r="E382" s="6" t="n"/>
+      <c r="F382" s="5" t="n"/>
+      <c r="G382" s="5" t="n"/>
+      <c r="H382" s="6" t="n"/>
+    </row>
+    <row r="383" hidden="1" outlineLevel="2">
+      <c r="A383" s="4" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="B383" s="5" t="n"/>
+      <c r="C383" s="6" t="n"/>
+      <c r="D383" s="6" t="n"/>
+      <c r="E383" s="6" t="n"/>
+      <c r="F383" s="5" t="n"/>
+      <c r="G383" s="5" t="n"/>
+      <c r="H383" s="6" t="n"/>
+    </row>
+    <row r="384" hidden="1" outlineLevel="2">
+      <c r="A384" s="4" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="B384" s="5" t="n"/>
+      <c r="C384" s="6" t="n"/>
+      <c r="D384" s="6" t="n"/>
+      <c r="E384" s="6" t="n"/>
+      <c r="F384" s="5" t="n"/>
+      <c r="G384" s="5" t="n"/>
+      <c r="H384" s="6" t="n"/>
+    </row>
+    <row r="385" hidden="1" outlineLevel="2">
+      <c r="A385" s="4" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="B385" s="5" t="n"/>
+      <c r="C385" s="6" t="n"/>
+      <c r="D385" s="6" t="n"/>
+      <c r="E385" s="6" t="n"/>
+      <c r="F385" s="5" t="n"/>
+      <c r="G385" s="5" t="n"/>
+      <c r="H385" s="6" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B386" t="inlineStr">
         <is>
           <t>Ende</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C386" t="inlineStr">
         <is>
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F386" t="n">
         <v>0</v>
       </c>
-      <c r="G18">
+      <c r="G386">
         <f>$C$3</f>
         <v/>
       </c>
